--- a/data/source/weekly/cs-en-us-pbsi.xlsx
+++ b/data/source/weekly/cs-en-us-pbsi.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>2</v>
-      </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>100</v>
+        <v>6</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G15" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="I15" s="14">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J15" s="14">
         <v>6</v>
       </c>
       <c r="K15" s="15">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="L15" s="15">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="M15" s="15">
-        <v>28.571428571428</v>
+        <v>114.285714285714</v>
       </c>
       <c r="N15" s="15">
-        <v>-43.75</v>
+        <v>-11.764705882352</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
         <v>6</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G16" s="14">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H16" s="15">
-        <v>-34.482758620689</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J16" s="14">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="K16" s="15">
-        <v>-9.090909090909</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="L16" s="15">
-        <v>15.384615384615</v>
+        <v>6.451612903225</v>
       </c>
       <c r="M16" s="15">
-        <v>-23.076923076923</v>
+        <v>-23.255813953488</v>
       </c>
       <c r="N16" s="15">
-        <v>-82.658959537572</v>
+        <v>-83.582089552238</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="D17" s="14">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E17" s="15">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="F17" s="14">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G17" s="14">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="H17" s="15">
-        <v>7.272727272727</v>
+        <v>-1.612903225806</v>
       </c>
       <c r="I17" s="14">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="J17" s="14">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="K17" s="15">
-        <v>9.876543209876</v>
+        <v>-0.990099009900</v>
       </c>
       <c r="L17" s="15">
-        <v>9.876543209876</v>
+        <v>-4.761904761904</v>
       </c>
       <c r="M17" s="15">
-        <v>97.777777777777</v>
+        <v>75.438596491228</v>
       </c>
       <c r="N17" s="15">
-        <v>-12.745098039215</v>
+        <v>-19.354838709677</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>6</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E18" s="15">
-        <v>20</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G18" s="14">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="H18" s="15">
-        <v>-72.093023255813</v>
+        <v>-67.346938775510</v>
       </c>
       <c r="I18" s="14">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J18" s="14">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="K18" s="15">
-        <v>-68.518518518518</v>
+        <v>-65.151515151515</v>
       </c>
       <c r="L18" s="15">
-        <v>-22.727272727272</v>
+        <v>-17.857142857142</v>
       </c>
       <c r="M18" s="15">
-        <v>-69.090909090909</v>
+        <v>-64.615384615384</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.480519480519</v>
+        <v>-93.66391184573</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D19" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E19" s="15">
-        <v>-9.090909090909</v>
+        <v>4.347826086956</v>
       </c>
       <c r="F19" s="14">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="G19" s="14">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H19" s="15">
-        <v>11.494252873563</v>
+        <v>1.111111111111</v>
       </c>
       <c r="I19" s="14">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="J19" s="14">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="K19" s="15">
-        <v>5.384615384615</v>
+        <v>5.228758169934</v>
       </c>
       <c r="L19" s="15">
-        <v>-16.463414634146</v>
+        <v>-18.686868686868</v>
       </c>
       <c r="M19" s="15">
-        <v>42.708333333333</v>
+        <v>43.75</v>
       </c>
       <c r="N19" s="15">
-        <v>-16.969696969697</v>
+        <v>-14.361702127659</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D20" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
         <v>-33.333333333333</v>
       </c>
       <c r="F20" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G20" s="14">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H20" s="15">
-        <v>-42.307692307692</v>
+        <v>-40.909090909090</v>
       </c>
       <c r="I20" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J20" s="14">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K20" s="15">
-        <v>-13.793103448275</v>
+        <v>-15.625</v>
       </c>
       <c r="L20" s="15">
-        <v>-7.407407407407</v>
+        <v>-3.571428571428</v>
       </c>
       <c r="M20" s="15">
-        <v>-35.897435897435</v>
+        <v>-37.209302325581</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.575221238938</v>
+        <v>-95.813953488372</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D21" s="17">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="E21" s="18">
-        <v>9.259259259259</v>
+        <v>-20.3125</v>
       </c>
       <c r="F21" s="17">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G21" s="17">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="H21" s="18">
-        <v>-15.510204081632</v>
+        <v>-18.110236220472</v>
       </c>
       <c r="I21" s="17">
-        <v>307</v>
+        <v>359</v>
       </c>
       <c r="J21" s="17">
-        <v>334</v>
+        <v>398</v>
       </c>
       <c r="K21" s="18">
-        <v>-8.083832335329</v>
+        <v>-9.798994974874</v>
       </c>
       <c r="L21" s="18">
-        <v>-5.828220858895</v>
+        <v>-9.343434343434</v>
       </c>
       <c r="M21" s="18">
-        <v>8.865248226950</v>
+        <v>9.451219512195</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.917293233082</v>
+        <v>-76.688311688311</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D23" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E23" s="15">
-        <v>300</v>
+        <v>-80</v>
       </c>
       <c r="F23" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G23" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H23" s="15">
-        <v>80</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I23" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J23" s="14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K23" s="15">
-        <v>25</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="L23" s="15">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="M23" s="15">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D24" s="14">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="E24" s="15">
-        <v>-42.857142857142</v>
+        <v>-23.684210526315</v>
       </c>
       <c r="F24" s="14">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="G24" s="14">
-        <v>355</v>
+        <v>339</v>
       </c>
       <c r="H24" s="15">
-        <v>-40</v>
+        <v>-41.002949852507</v>
       </c>
       <c r="I24" s="14">
-        <v>313</v>
+        <v>372</v>
       </c>
       <c r="J24" s="14">
-        <v>488</v>
+        <v>564</v>
       </c>
       <c r="K24" s="15">
-        <v>-35.860655737704</v>
+        <v>-34.042553191489</v>
       </c>
       <c r="L24" s="15">
-        <v>-31.057268722467</v>
+        <v>-32.608695652173</v>
       </c>
       <c r="M24" s="15">
-        <v>-19.537275064267</v>
+        <v>-13.888888888888</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D25" s="14">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E25" s="15">
-        <v>-34</v>
+        <v>-40.425531914893</v>
       </c>
       <c r="F25" s="14">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="G25" s="14">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="H25" s="15">
-        <v>-47.136563876652</v>
+        <v>-49.771689497716</v>
       </c>
       <c r="I25" s="14">
-        <v>161</v>
+        <v>189</v>
       </c>
       <c r="J25" s="14">
-        <v>304</v>
+        <v>351</v>
       </c>
       <c r="K25" s="15">
-        <v>-47.039473684210</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="L25" s="15">
-        <v>-26.146788990825</v>
+        <v>-33.916083916083</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="D26" s="14">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E26" s="15">
-        <v>-16.129032258064</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="G26" s="14">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H26" s="15">
-        <v>-14.4</v>
+        <v>-4.065040650406</v>
       </c>
       <c r="I26" s="14">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="J26" s="14">
-        <v>182</v>
+        <v>212</v>
       </c>
       <c r="K26" s="15">
-        <v>-23.076923076923</v>
+        <v>-15.094339622641</v>
       </c>
       <c r="L26" s="15">
-        <v>-9.090909090909</v>
+        <v>-4.255319148936</v>
       </c>
       <c r="M26" s="15">
-        <v>-22.651933701657</v>
+        <v>-14.691943127962</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>3</v>
-      </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>200</v>
+        <v>7</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G27" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H27" s="15">
-        <v>12.5</v>
+        <v>116.666666666667</v>
       </c>
       <c r="I27" s="14">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J27" s="14">
         <v>9</v>
       </c>
       <c r="K27" s="15">
-        <v>44.444444444444</v>
+        <v>133.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>8.333333333333</v>
+        <v>61.538461538461</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D28" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E28" s="15">
-        <v>-50</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F28" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G28" s="14">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H28" s="15">
-        <v>-25</v>
+        <v>-55</v>
       </c>
       <c r="I28" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J28" s="14">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="K28" s="15">
-        <v>-31.818181818181</v>
+        <v>-37.931034482758</v>
       </c>
       <c r="L28" s="15">
-        <v>-11.764705882352</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,29 +1469,29 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15">
+        <v>-100</v>
       </c>
       <c r="I29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K29" s="13" t="s">
-        <v>21</v>
+      <c r="J29" s="14">
+        <v>1</v>
+      </c>
+      <c r="K29" s="15">
+        <v>-100</v>
       </c>
       <c r="L29" s="15">
         <v>-100</v>
@@ -1510,29 +1510,29 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>-100</v>
       </c>
       <c r="I30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K30" s="13" t="s">
-        <v>21</v>
+      <c r="J30" s="14">
+        <v>1</v>
+      </c>
+      <c r="K30" s="15">
+        <v>-100</v>
       </c>
       <c r="L30" s="15">
         <v>-100</v>
@@ -1548,8 +1548,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="14">
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1566,8 +1566,8 @@
       <c r="H31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I31" s="13" t="s">
-        <v>20</v>
+      <c r="I31" s="14">
+        <v>1</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>
@@ -1576,7 +1576,7 @@
         <v>21</v>
       </c>
       <c r="L31" s="15">
-        <v>-100</v>
+        <v>-80</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-pbsi.xlsx
+++ b/data/source/weekly/cs-en-us-pbsi.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -893,13 +893,13 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>6</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D15" s="14">
+        <v>2</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-50</v>
       </c>
       <c r="F15" s="14">
         <v>9</v>
@@ -911,22 +911,22 @@
         <v>125</v>
       </c>
       <c r="I15" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J15" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K15" s="15">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="L15" s="15">
-        <v>200</v>
+        <v>128.571428571429</v>
       </c>
       <c r="M15" s="15">
-        <v>114.285714285714</v>
+        <v>128.571428571429</v>
       </c>
       <c r="N15" s="15">
-        <v>-11.764705882352</v>
+        <v>-5.882352941176</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
         <v>6</v>
       </c>
       <c r="E16" s="15">
-        <v>-50</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F16" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G16" s="14">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H16" s="15">
-        <v>-33.333333333333</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="I16" s="14">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J16" s="14">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="K16" s="15">
-        <v>-15.384615384615</v>
+        <v>-15.555555555555</v>
       </c>
       <c r="L16" s="15">
-        <v>6.451612903225</v>
+        <v>2.702702702702</v>
       </c>
       <c r="M16" s="15">
-        <v>-23.255813953488</v>
+        <v>-25.490196078431</v>
       </c>
       <c r="N16" s="15">
-        <v>-83.582089552238</v>
+        <v>-83.185840707964</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D17" s="14">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E17" s="15">
-        <v>-50</v>
+        <v>-12.5</v>
       </c>
       <c r="F17" s="14">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G17" s="14">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="H17" s="15">
-        <v>-1.612903225806</v>
+        <v>-13.043478260869</v>
       </c>
       <c r="I17" s="14">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="J17" s="14">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="K17" s="15">
-        <v>-0.990099009900</v>
+        <v>-1.709401709401</v>
       </c>
       <c r="L17" s="15">
-        <v>-4.761904761904</v>
+        <v>-6.504065040650</v>
       </c>
       <c r="M17" s="15">
-        <v>75.438596491228</v>
+        <v>71.641791044776</v>
       </c>
       <c r="N17" s="15">
-        <v>-19.354838709677</v>
+        <v>-16.058394160583</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>6</v>
       </c>
       <c r="D18" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E18" s="15">
+        <v>-45.454545454545</v>
+      </c>
+      <c r="F18" s="14">
+        <v>22</v>
+      </c>
+      <c r="G18" s="14">
+        <v>44</v>
+      </c>
+      <c r="H18" s="15">
         <v>-50</v>
       </c>
-      <c r="F18" s="14">
-        <v>16</v>
-      </c>
-      <c r="G18" s="14">
-        <v>49</v>
-      </c>
-      <c r="H18" s="15">
-        <v>-67.346938775510</v>
-      </c>
       <c r="I18" s="14">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J18" s="14">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="K18" s="15">
-        <v>-65.151515151515</v>
+        <v>-62.337662337662</v>
       </c>
       <c r="L18" s="15">
-        <v>-17.857142857142</v>
+        <v>-17.142857142857</v>
       </c>
       <c r="M18" s="15">
-        <v>-64.615384615384</v>
+        <v>-58.571428571428</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.66391184573</v>
+        <v>-93.394077448747</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D19" s="14">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E19" s="15">
-        <v>4.347826086956</v>
+        <v>-3.571428571428</v>
       </c>
       <c r="F19" s="14">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G19" s="14">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="H19" s="15">
-        <v>1.111111111111</v>
+        <v>-4.040404040404</v>
       </c>
       <c r="I19" s="14">
-        <v>161</v>
+        <v>187</v>
       </c>
       <c r="J19" s="14">
-        <v>153</v>
+        <v>181</v>
       </c>
       <c r="K19" s="15">
-        <v>5.228758169934</v>
+        <v>3.314917127071</v>
       </c>
       <c r="L19" s="15">
-        <v>-18.686868686868</v>
+        <v>-20.085470085470</v>
       </c>
       <c r="M19" s="15">
-        <v>43.75</v>
+        <v>44.961240310077</v>
       </c>
       <c r="N19" s="15">
-        <v>-14.361702127659</v>
+        <v>-13.023255813953</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E20" s="15">
-        <v>-33.333333333333</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="F20" s="14">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G20" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H20" s="15">
-        <v>-40.909090909090</v>
+        <v>-62.5</v>
       </c>
       <c r="I20" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J20" s="14">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="K20" s="15">
-        <v>-15.625</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="L20" s="15">
-        <v>-3.571428571428</v>
+        <v>-3.448275862068</v>
       </c>
       <c r="M20" s="15">
-        <v>-37.209302325581</v>
+        <v>-40.425531914893</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.813953488372</v>
+        <v>-96.211096075778</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D21" s="17">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E21" s="18">
-        <v>-20.3125</v>
+        <v>-21.739130434782</v>
       </c>
       <c r="F21" s="17">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="G21" s="17">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="H21" s="18">
-        <v>-18.110236220472</v>
+        <v>-18.320610687022</v>
       </c>
       <c r="I21" s="17">
-        <v>359</v>
+        <v>413</v>
       </c>
       <c r="J21" s="17">
-        <v>398</v>
+        <v>467</v>
       </c>
       <c r="K21" s="18">
-        <v>-9.798994974874</v>
+        <v>-11.563169164882</v>
       </c>
       <c r="L21" s="18">
-        <v>-9.343434343434</v>
+        <v>-11.373390557939</v>
       </c>
       <c r="M21" s="18">
-        <v>9.451219512195</v>
+        <v>11.021505376344</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.688311688311</v>
+        <v>-76.745495495495</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D23" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E23" s="15">
-        <v>-80</v>
+        <v>300</v>
       </c>
       <c r="F23" s="14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G23" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H23" s="15">
-        <v>14.285714285714</v>
+        <v>44.444444444444</v>
       </c>
       <c r="I23" s="14">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="J23" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K23" s="15">
-        <v>-15.384615384615</v>
+        <v>26.666666666666</v>
       </c>
       <c r="L23" s="15">
-        <v>37.5</v>
+        <v>111.111111111111</v>
       </c>
       <c r="M23" s="15">
-        <v>120</v>
+        <v>216.666666666667</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D24" s="14">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="E24" s="15">
-        <v>-23.684210526315</v>
+        <v>-37.078651685393</v>
       </c>
       <c r="F24" s="14">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="G24" s="14">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="H24" s="15">
-        <v>-41.002949852507</v>
+        <v>-38.192419825072</v>
       </c>
       <c r="I24" s="14">
-        <v>372</v>
+        <v>426</v>
       </c>
       <c r="J24" s="14">
-        <v>564</v>
+        <v>653</v>
       </c>
       <c r="K24" s="15">
-        <v>-34.042553191489</v>
+        <v>-34.762633996937</v>
       </c>
       <c r="L24" s="15">
-        <v>-32.608695652173</v>
+        <v>-32.273449920508</v>
       </c>
       <c r="M24" s="15">
-        <v>-13.888888888888</v>
+        <v>-11.801242236024</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D25" s="14">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E25" s="15">
-        <v>-40.425531914893</v>
+        <v>-46.938775510204</v>
       </c>
       <c r="F25" s="14">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G25" s="14">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="H25" s="15">
-        <v>-49.771689497716</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="I25" s="14">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="J25" s="14">
-        <v>351</v>
+        <v>400</v>
       </c>
       <c r="K25" s="15">
-        <v>-46.153846153846</v>
+        <v>-46.25</v>
       </c>
       <c r="L25" s="15">
-        <v>-33.916083916083</v>
+        <v>-35.820895522388</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D26" s="14">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E26" s="15">
-        <v>33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="F26" s="14">
+        <v>131</v>
+      </c>
+      <c r="G26" s="14">
         <v>118</v>
       </c>
-      <c r="G26" s="14">
-        <v>123</v>
-      </c>
       <c r="H26" s="15">
-        <v>-4.065040650406</v>
+        <v>11.016949152542</v>
       </c>
       <c r="I26" s="14">
-        <v>180</v>
+        <v>217</v>
       </c>
       <c r="J26" s="14">
-        <v>212</v>
+        <v>238</v>
       </c>
       <c r="K26" s="15">
-        <v>-15.094339622641</v>
+        <v>-8.823529411764</v>
       </c>
       <c r="L26" s="15">
-        <v>-4.255319148936</v>
+        <v>-1.363636363636</v>
       </c>
       <c r="M26" s="15">
-        <v>-14.691943127962</v>
+        <v>-9.583333333333</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>7</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D27" s="14">
+        <v>2</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-50</v>
       </c>
       <c r="F27" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G27" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H27" s="15">
-        <v>116.666666666667</v>
+        <v>140</v>
       </c>
       <c r="I27" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J27" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K27" s="15">
-        <v>133.333333333333</v>
+        <v>100</v>
       </c>
       <c r="L27" s="15">
-        <v>61.538461538461</v>
+        <v>29.411764705882</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D28" s="14">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>-57.142857142857</v>
+        <v>300</v>
       </c>
       <c r="F28" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G28" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H28" s="15">
-        <v>-55</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="I28" s="14">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J28" s="14">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K28" s="15">
-        <v>-37.931034482758</v>
+        <v>-19.354838709677</v>
       </c>
       <c r="L28" s="15">
-        <v>-14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,11 +1469,11 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
@@ -1510,11 +1510,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
@@ -1548,8 +1548,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>1</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-pbsi.xlsx
+++ b/data/source/weekly/cs-en-us-pbsi.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -902,31 +902,31 @@
         <v>-50</v>
       </c>
       <c r="F15" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G15" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H15" s="15">
+        <v>120</v>
+      </c>
+      <c r="I15" s="14">
+        <v>18</v>
+      </c>
+      <c r="J15" s="14">
+        <v>10</v>
+      </c>
+      <c r="K15" s="15">
+        <v>80</v>
+      </c>
+      <c r="L15" s="15">
         <v>125</v>
       </c>
-      <c r="I15" s="14">
-        <v>16</v>
-      </c>
-      <c r="J15" s="14">
-        <v>8</v>
-      </c>
-      <c r="K15" s="15">
+      <c r="M15" s="15">
         <v>100</v>
       </c>
-      <c r="L15" s="15">
-        <v>128.571428571429</v>
-      </c>
-      <c r="M15" s="15">
-        <v>128.571428571429</v>
-      </c>
       <c r="N15" s="15">
-        <v>-5.882352941176</v>
+        <v>-5.263157894736</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
         <v>6</v>
       </c>
       <c r="E16" s="15">
-        <v>-16.666666666666</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F16" s="14">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G16" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H16" s="15">
-        <v>-13.636363636363</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J16" s="14">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="K16" s="15">
-        <v>-15.555555555555</v>
+        <v>-21.568627450980</v>
       </c>
       <c r="L16" s="15">
-        <v>2.702702702702</v>
+        <v>-14.893617021276</v>
       </c>
       <c r="M16" s="15">
-        <v>-25.490196078431</v>
+        <v>-25.925925925925</v>
       </c>
       <c r="N16" s="15">
-        <v>-83.185840707964</v>
+        <v>-84.126984126984</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D17" s="14">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E17" s="15">
-        <v>-12.5</v>
+        <v>-26.086956521739</v>
       </c>
       <c r="F17" s="14">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G17" s="14">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="H17" s="15">
-        <v>-13.043478260869</v>
+        <v>-10.958904109589</v>
       </c>
       <c r="I17" s="14">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="J17" s="14">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="K17" s="15">
-        <v>-1.709401709401</v>
+        <v>-5</v>
       </c>
       <c r="L17" s="15">
-        <v>-6.504065040650</v>
+        <v>-13.071895424836</v>
       </c>
       <c r="M17" s="15">
-        <v>71.641791044776</v>
+        <v>70.512820512820</v>
       </c>
       <c r="N17" s="15">
-        <v>-16.058394160583</v>
+        <v>-18.404907975460</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E18" s="15">
-        <v>-45.454545454545</v>
+        <v>-87.5</v>
       </c>
       <c r="F18" s="14">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G18" s="14">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="H18" s="15">
-        <v>-50</v>
+        <v>-47.222222222222</v>
       </c>
       <c r="I18" s="14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J18" s="14">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K18" s="15">
-        <v>-62.337662337662</v>
+        <v>-64.705882352941</v>
       </c>
       <c r="L18" s="15">
-        <v>-17.142857142857</v>
+        <v>-31.818181818181</v>
       </c>
       <c r="M18" s="15">
-        <v>-58.571428571428</v>
+        <v>-63.855421686747</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.394077448747</v>
+        <v>-94.219653179190</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D19" s="14">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E19" s="15">
-        <v>-3.571428571428</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="F19" s="14">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G19" s="14">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="H19" s="15">
-        <v>-4.040404040404</v>
+        <v>-13.084112149532</v>
       </c>
       <c r="I19" s="14">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="J19" s="14">
-        <v>181</v>
+        <v>215</v>
       </c>
       <c r="K19" s="15">
-        <v>3.314917127071</v>
+        <v>-3.255813953488</v>
       </c>
       <c r="L19" s="15">
-        <v>-20.085470085470</v>
+        <v>-22.388059701492</v>
       </c>
       <c r="M19" s="15">
-        <v>44.961240310077</v>
+        <v>45.454545454545</v>
       </c>
       <c r="N19" s="15">
-        <v>-13.023255813953</v>
+        <v>-15.789473684210</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>-83.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G20" s="14">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H20" s="15">
-        <v>-62.5</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="I20" s="14">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J20" s="14">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K20" s="15">
-        <v>-26.315789473684</v>
+        <v>-24.390243902439</v>
       </c>
       <c r="L20" s="15">
-        <v>-3.448275862068</v>
+        <v>-13.888888888888</v>
       </c>
       <c r="M20" s="15">
-        <v>-40.425531914893</v>
+        <v>-38</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.211096075778</v>
+        <v>-96.256038647343</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="D21" s="17">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="E21" s="18">
-        <v>-21.739130434782</v>
+        <v>-42.105263157894</v>
       </c>
       <c r="F21" s="17">
         <v>214</v>
       </c>
       <c r="G21" s="17">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H21" s="18">
-        <v>-18.320610687022</v>
+        <v>-18.631178707224</v>
       </c>
       <c r="I21" s="17">
-        <v>413</v>
+        <v>460</v>
       </c>
       <c r="J21" s="17">
-        <v>467</v>
+        <v>543</v>
       </c>
       <c r="K21" s="18">
-        <v>-11.563169164882</v>
+        <v>-15.285451197053</v>
       </c>
       <c r="L21" s="18">
-        <v>-11.373390557939</v>
+        <v>-17.414721723518</v>
       </c>
       <c r="M21" s="18">
-        <v>11.021505376344</v>
+        <v>9.785202863961</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.745495495495</v>
+        <v>-77.373339891785</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1220,35 +1220,35 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>8</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E23" s="15">
-        <v>300</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
         <v>13</v>
       </c>
       <c r="G23" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H23" s="15">
-        <v>44.444444444444</v>
+        <v>8.333333333333</v>
       </c>
       <c r="I23" s="14">
         <v>19</v>
       </c>
       <c r="J23" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K23" s="15">
-        <v>26.666666666666</v>
+        <v>0</v>
       </c>
       <c r="L23" s="15">
-        <v>111.111111111111</v>
+        <v>90</v>
       </c>
       <c r="M23" s="15">
         <v>216.666666666667</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="D24" s="14">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E24" s="15">
-        <v>-37.078651685393</v>
+        <v>-58.064516129032</v>
       </c>
       <c r="F24" s="14">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="G24" s="14">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="H24" s="15">
-        <v>-38.192419825072</v>
+        <v>-41.547277936962</v>
       </c>
       <c r="I24" s="14">
-        <v>426</v>
+        <v>464</v>
       </c>
       <c r="J24" s="14">
-        <v>653</v>
+        <v>746</v>
       </c>
       <c r="K24" s="15">
-        <v>-34.762633996937</v>
+        <v>-37.801608579088</v>
       </c>
       <c r="L24" s="15">
-        <v>-32.273449920508</v>
+        <v>-35.734072022160</v>
       </c>
       <c r="M24" s="15">
-        <v>-11.801242236024</v>
+        <v>-11.281070745697</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D25" s="14">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E25" s="15">
-        <v>-46.938775510204</v>
+        <v>-57.692307692307</v>
       </c>
       <c r="F25" s="14">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="G25" s="14">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="H25" s="15">
-        <v>-46.153846153846</v>
+        <v>-44.949494949494</v>
       </c>
       <c r="I25" s="14">
-        <v>215</v>
+        <v>237</v>
       </c>
       <c r="J25" s="14">
-        <v>400</v>
+        <v>452</v>
       </c>
       <c r="K25" s="15">
-        <v>-46.25</v>
+        <v>-47.566371681415</v>
       </c>
       <c r="L25" s="15">
-        <v>-35.820895522388</v>
+        <v>-40.302267002518</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D26" s="14">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E26" s="15">
-        <v>50</v>
+        <v>3.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="G26" s="14">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H26" s="15">
-        <v>11.016949152542</v>
+        <v>17.948717948717</v>
       </c>
       <c r="I26" s="14">
-        <v>217</v>
+        <v>252</v>
       </c>
       <c r="J26" s="14">
-        <v>238</v>
+        <v>268</v>
       </c>
       <c r="K26" s="15">
-        <v>-8.823529411764</v>
+        <v>-5.970149253731</v>
       </c>
       <c r="L26" s="15">
-        <v>-1.363636363636</v>
+        <v>-6.319702602230</v>
       </c>
       <c r="M26" s="15">
-        <v>-9.583333333333</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,25 +1394,25 @@
         <v>-50</v>
       </c>
       <c r="F27" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G27" s="14">
         <v>5</v>
       </c>
       <c r="H27" s="15">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="I27" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J27" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K27" s="15">
-        <v>100</v>
+        <v>84.615384615384</v>
       </c>
       <c r="L27" s="15">
-        <v>29.411764705882</v>
+        <v>26.315789473684</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E28" s="15">
-        <v>300</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F28" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G28" s="14">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H28" s="15">
-        <v>-27.777777777777</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="I28" s="14">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J28" s="14">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="K28" s="15">
-        <v>-19.354838709677</v>
+        <v>-22.5</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>10.714285714285</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,29 +1551,29 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="14">
         <v>1</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="14">
+        <v>1</v>
+      </c>
+      <c r="H31" s="15">
+        <v>0</v>
       </c>
       <c r="I31" s="14">
         <v>1</v>
       </c>
-      <c r="J31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>21</v>
+      <c r="J31" s="14">
+        <v>1</v>
+      </c>
+      <c r="K31" s="15">
+        <v>0</v>
       </c>
       <c r="L31" s="15">
         <v>-80</v>

--- a/data/source/weekly/cs-en-us-pbsi.xlsx
+++ b/data/source/weekly/cs-en-us-pbsi.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>1</v>
-      </c>
-      <c r="D15" s="14">
-        <v>2</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-50</v>
+        <v>5</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G15" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H15" s="15">
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="I15" s="14">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J15" s="14">
         <v>10</v>
       </c>
       <c r="K15" s="15">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="L15" s="15">
-        <v>125</v>
+        <v>109.090909090909</v>
       </c>
       <c r="M15" s="15">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="N15" s="15">
-        <v>-5.263157894736</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>-66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="F16" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G16" s="14">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H16" s="15">
-        <v>-33.333333333333</v>
+        <v>-31.818181818181</v>
       </c>
       <c r="I16" s="14">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J16" s="14">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K16" s="15">
-        <v>-21.568627450980</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="L16" s="15">
-        <v>-14.893617021276</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="M16" s="15">
-        <v>-25.925925925925</v>
+        <v>-27.419354838709</v>
       </c>
       <c r="N16" s="15">
-        <v>-84.126984126984</v>
+        <v>-84.589041095890</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D17" s="14">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E17" s="15">
-        <v>-26.086956521739</v>
+        <v>-38.095238095238</v>
       </c>
       <c r="F17" s="14">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="G17" s="14">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="H17" s="15">
-        <v>-10.958904109589</v>
+        <v>-27.5</v>
       </c>
       <c r="I17" s="14">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="J17" s="14">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="K17" s="15">
-        <v>-5</v>
+        <v>-8.074534161490</v>
       </c>
       <c r="L17" s="15">
-        <v>-13.071895424836</v>
+        <v>-20.430107526881</v>
       </c>
       <c r="M17" s="15">
-        <v>70.512820512820</v>
+        <v>59.139784946236</v>
       </c>
       <c r="N17" s="15">
-        <v>-18.404907975460</v>
+        <v>-20.855614973262</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D18" s="14">
         <v>8</v>
       </c>
       <c r="E18" s="15">
-        <v>-87.5</v>
+        <v>-37.5</v>
       </c>
       <c r="F18" s="14">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G18" s="14">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H18" s="15">
-        <v>-47.222222222222</v>
+        <v>-56.410256410256</v>
       </c>
       <c r="I18" s="14">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J18" s="14">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="K18" s="15">
-        <v>-64.705882352941</v>
+        <v>-63.440860215053</v>
       </c>
       <c r="L18" s="15">
-        <v>-31.818181818181</v>
+        <v>-30.612244897959</v>
       </c>
       <c r="M18" s="15">
-        <v>-63.855421686747</v>
+        <v>-62.222222222222</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.219653179190</v>
+        <v>-94.342762063228</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="D19" s="14">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E19" s="15">
-        <v>-41.176470588235</v>
+        <v>16</v>
       </c>
       <c r="F19" s="14">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="G19" s="14">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="H19" s="15">
-        <v>-13.084112149532</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="I19" s="14">
-        <v>208</v>
+        <v>237</v>
       </c>
       <c r="J19" s="14">
-        <v>215</v>
+        <v>240</v>
       </c>
       <c r="K19" s="15">
-        <v>-3.255813953488</v>
+        <v>-1.25</v>
       </c>
       <c r="L19" s="15">
-        <v>-22.388059701492</v>
+        <v>-20.735785953177</v>
       </c>
       <c r="M19" s="15">
-        <v>45.454545454545</v>
+        <v>48.125</v>
       </c>
       <c r="N19" s="15">
-        <v>-15.789473684210</v>
+        <v>-13.818181818181</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D20" s="14">
         <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F20" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G20" s="14">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H20" s="15">
-        <v>-44.444444444444</v>
+        <v>-40</v>
       </c>
       <c r="I20" s="14">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J20" s="14">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="K20" s="15">
-        <v>-24.390243902439</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="L20" s="15">
-        <v>-13.888888888888</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="M20" s="15">
-        <v>-38</v>
+        <v>-37.037037037037</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.256038647343</v>
+        <v>-96.316359696641</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D21" s="17">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="E21" s="18">
-        <v>-42.105263157894</v>
+        <v>-3.278688524590</v>
       </c>
       <c r="F21" s="17">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G21" s="17">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="H21" s="18">
-        <v>-18.631178707224</v>
+        <v>-21.111111111111</v>
       </c>
       <c r="I21" s="17">
-        <v>460</v>
+        <v>521</v>
       </c>
       <c r="J21" s="17">
-        <v>543</v>
+        <v>604</v>
       </c>
       <c r="K21" s="18">
-        <v>-15.285451197053</v>
+        <v>-13.741721854304</v>
       </c>
       <c r="L21" s="18">
-        <v>-17.414721723518</v>
+        <v>-18.466353677621</v>
       </c>
       <c r="M21" s="18">
-        <v>9.785202863961</v>
+        <v>10.615711252653</v>
       </c>
       <c r="N21" s="18">
-        <v>-77.373339891785</v>
+        <v>-77.377333912288</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1224,34 +1224,34 @@
         <v>20</v>
       </c>
       <c r="D23" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E23" s="15">
         <v>-100</v>
       </c>
       <c r="F23" s="14">
+        <v>9</v>
+      </c>
+      <c r="G23" s="14">
         <v>13</v>
       </c>
-      <c r="G23" s="14">
-        <v>12</v>
-      </c>
       <c r="H23" s="15">
-        <v>8.333333333333</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="I23" s="14">
         <v>19</v>
       </c>
       <c r="J23" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K23" s="15">
-        <v>0</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="L23" s="15">
-        <v>90</v>
+        <v>72.727272727272</v>
       </c>
       <c r="M23" s="15">
-        <v>216.666666666667</v>
+        <v>171.428571428571</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="D24" s="14">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="E24" s="15">
-        <v>-58.064516129032</v>
+        <v>-7.8125</v>
       </c>
       <c r="F24" s="14">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="G24" s="14">
-        <v>349</v>
+        <v>321</v>
       </c>
       <c r="H24" s="15">
-        <v>-41.547277936962</v>
+        <v>-34.267912772585</v>
       </c>
       <c r="I24" s="14">
-        <v>464</v>
+        <v>523</v>
       </c>
       <c r="J24" s="14">
-        <v>746</v>
+        <v>809</v>
       </c>
       <c r="K24" s="15">
-        <v>-37.801608579088</v>
+        <v>-35.352286773794</v>
       </c>
       <c r="L24" s="15">
-        <v>-35.734072022160</v>
+        <v>-35.985312117503</v>
       </c>
       <c r="M24" s="15">
-        <v>-11.281070745697</v>
+        <v>-10.902896081771</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D25" s="14">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="E25" s="15">
-        <v>-57.692307692307</v>
+        <v>-24.242424242424</v>
       </c>
       <c r="F25" s="14">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="G25" s="14">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="H25" s="15">
-        <v>-44.949494949494</v>
+        <v>-44.198895027624</v>
       </c>
       <c r="I25" s="14">
-        <v>237</v>
+        <v>262</v>
       </c>
       <c r="J25" s="14">
-        <v>452</v>
+        <v>485</v>
       </c>
       <c r="K25" s="15">
-        <v>-47.566371681415</v>
+        <v>-45.979381443299</v>
       </c>
       <c r="L25" s="15">
-        <v>-40.302267002518</v>
+        <v>-41.906873614190</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D26" s="14">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="E26" s="15">
-        <v>3.333333333333</v>
+        <v>-30.952380952381</v>
       </c>
       <c r="F26" s="14">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="G26" s="14">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="H26" s="15">
-        <v>17.948717948717</v>
+        <v>10.9375</v>
       </c>
       <c r="I26" s="14">
-        <v>252</v>
+        <v>281</v>
       </c>
       <c r="J26" s="14">
-        <v>268</v>
+        <v>310</v>
       </c>
       <c r="K26" s="15">
-        <v>-5.970149253731</v>
+        <v>-9.354838709677</v>
       </c>
       <c r="L26" s="15">
-        <v>-6.319702602230</v>
+        <v>-6.644518272425</v>
       </c>
       <c r="M26" s="15">
-        <v>-5.263157894736</v>
+        <v>-7.868852459016</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
+        <v>6</v>
+      </c>
+      <c r="D27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="14">
-        <v>2</v>
-      </c>
       <c r="E27" s="15">
-        <v>-50</v>
+        <v>500</v>
       </c>
       <c r="F27" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G27" s="14">
         <v>5</v>
       </c>
       <c r="H27" s="15">
-        <v>160</v>
+        <v>220</v>
       </c>
       <c r="I27" s="14">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J27" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K27" s="15">
-        <v>84.615384615384</v>
+        <v>114.285714285714</v>
       </c>
       <c r="L27" s="15">
-        <v>26.315789473684</v>
+        <v>36.363636363636</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D28" s="14">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E28" s="15">
-        <v>-44.444444444444</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F28" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G28" s="14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H28" s="15">
-        <v>-22.727272727272</v>
+        <v>-4.761904761904</v>
       </c>
       <c r="I28" s="14">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J28" s="14">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K28" s="15">
-        <v>-22.5</v>
+        <v>-18.604651162790</v>
       </c>
       <c r="L28" s="15">
-        <v>10.714285714285</v>
+        <v>12.903225806451</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>2</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,40 +1475,40 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="14">
+        <v>2</v>
       </c>
       <c r="G29" s="14">
         <v>1</v>
       </c>
       <c r="H29" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I29" s="13" t="s">
-        <v>20</v>
+        <v>100</v>
+      </c>
+      <c r="I29" s="14">
+        <v>2</v>
       </c>
       <c r="J29" s="14">
         <v>1</v>
       </c>
       <c r="K29" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L29" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="M29" s="15">
-        <v>-100</v>
+        <v>-60</v>
       </c>
       <c r="N29" s="15">
-        <v>-100</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>2</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,67 +1516,67 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="14">
+        <v>2</v>
       </c>
       <c r="G30" s="14">
         <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I30" s="13" t="s">
-        <v>20</v>
+        <v>100</v>
+      </c>
+      <c r="I30" s="14">
+        <v>2</v>
       </c>
       <c r="J30" s="14">
         <v>1</v>
       </c>
       <c r="K30" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L30" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="M30" s="15">
-        <v>-100</v>
+        <v>-60</v>
       </c>
       <c r="N30" s="15">
-        <v>-100</v>
+        <v>-85.714285714285</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="14">
+        <v>1</v>
+      </c>
+      <c r="D31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31" s="14">
         <v>1</v>
       </c>
       <c r="H31" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" s="14">
         <v>1</v>
       </c>
       <c r="K31" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L31" s="15">
-        <v>-80</v>
+        <v>-60</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1610,29 +1610,29 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>21</v>
+      <c r="D33" s="14">
+        <v>1</v>
+      </c>
+      <c r="E33" s="15">
+        <v>-100</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>21</v>
+      <c r="G33" s="14">
+        <v>1</v>
+      </c>
+      <c r="H33" s="15">
+        <v>-100</v>
       </c>
       <c r="I33" s="14">
         <v>3</v>
       </c>
       <c r="J33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K33" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="L33" s="15">
         <v>200</v>

--- a/data/source/weekly/cs-en-us-pbsi.xlsx
+++ b/data/source/weekly/cs-en-us-pbsi.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F15" s="14">
+        <v>7</v>
+      </c>
+      <c r="G15" s="14">
         <v>5</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="14">
-        <v>14</v>
-      </c>
-      <c r="G15" s="14">
-        <v>4</v>
-      </c>
       <c r="H15" s="15">
-        <v>250</v>
+        <v>40</v>
       </c>
       <c r="I15" s="14">
         <v>23</v>
       </c>
       <c r="J15" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K15" s="15">
-        <v>130</v>
+        <v>109.090909090909</v>
       </c>
       <c r="L15" s="15">
+        <v>91.666666666666</v>
+      </c>
+      <c r="M15" s="15">
         <v>109.090909090909</v>
       </c>
-      <c r="M15" s="15">
-        <v>130</v>
-      </c>
       <c r="N15" s="15">
-        <v>15</v>
+        <v>9.523809523809</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>5</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>25</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F16" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G16" s="14">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H16" s="15">
-        <v>-31.818181818181</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="I16" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J16" s="14">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K16" s="15">
-        <v>-18.181818181818</v>
+        <v>-13.793103448275</v>
       </c>
       <c r="L16" s="15">
-        <v>-11.764705882352</v>
+        <v>-3.846153846153</v>
       </c>
       <c r="M16" s="15">
-        <v>-27.419354838709</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="N16" s="15">
-        <v>-84.589041095890</v>
+        <v>-84.076433121019</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="D17" s="14">
         <v>21</v>
       </c>
       <c r="E17" s="15">
-        <v>-38.095238095238</v>
+        <v>38.095238095238</v>
       </c>
       <c r="F17" s="14">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="G17" s="14">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H17" s="15">
-        <v>-27.5</v>
+        <v>-4.938271604938</v>
       </c>
       <c r="I17" s="14">
-        <v>148</v>
+        <v>179</v>
       </c>
       <c r="J17" s="14">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="K17" s="15">
-        <v>-8.074534161490</v>
+        <v>-1.648351648351</v>
       </c>
       <c r="L17" s="15">
-        <v>-20.430107526881</v>
+        <v>-12.682926829268</v>
       </c>
       <c r="M17" s="15">
-        <v>59.139784946236</v>
+        <v>75.490196078431</v>
       </c>
       <c r="N17" s="15">
-        <v>-20.855614973262</v>
+        <v>-11.822660098522</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>-37.5</v>
+        <v>-25</v>
       </c>
       <c r="F18" s="14">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G18" s="14">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="H18" s="15">
-        <v>-56.410256410256</v>
+        <v>-58.064516129032</v>
       </c>
       <c r="I18" s="14">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="J18" s="14">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="K18" s="15">
-        <v>-63.440860215053</v>
+        <v>-60.824742268041</v>
       </c>
       <c r="L18" s="15">
-        <v>-30.612244897959</v>
+        <v>-28.301886792452</v>
       </c>
       <c r="M18" s="15">
-        <v>-62.222222222222</v>
+        <v>-61.616161616161</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.342762063228</v>
+        <v>-94.259818731117</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D19" s="14">
         <v>25</v>
       </c>
       <c r="E19" s="15">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F19" s="14">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="G19" s="14">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H19" s="15">
-        <v>-9.090909090909</v>
+        <v>-5.357142857142</v>
       </c>
       <c r="I19" s="14">
-        <v>237</v>
+        <v>268</v>
       </c>
       <c r="J19" s="14">
-        <v>240</v>
+        <v>265</v>
       </c>
       <c r="K19" s="15">
-        <v>-1.25</v>
+        <v>1.132075471698</v>
       </c>
       <c r="L19" s="15">
-        <v>-20.735785953177</v>
+        <v>-19.033232628398</v>
       </c>
       <c r="M19" s="15">
-        <v>48.125</v>
+        <v>54.913294797687</v>
       </c>
       <c r="N19" s="15">
-        <v>-13.818181818181</v>
+        <v>-8.843537414965</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>5</v>
+      </c>
+      <c r="D20" s="14">
         <v>2</v>
       </c>
-      <c r="D20" s="14">
-        <v>3</v>
-      </c>
       <c r="E20" s="15">
-        <v>-33.333333333333</v>
+        <v>150</v>
       </c>
       <c r="F20" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G20" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H20" s="15">
-        <v>-40</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I20" s="14">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J20" s="14">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K20" s="15">
-        <v>-22.727272727272</v>
+        <v>-15.217391304347</v>
       </c>
       <c r="L20" s="15">
-        <v>-19.047619047619</v>
+        <v>-15.217391304347</v>
       </c>
       <c r="M20" s="15">
-        <v>-37.037037037037</v>
+        <v>-35</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.316359696641</v>
+        <v>-96.130952380952</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="D21" s="17">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E21" s="18">
-        <v>-3.278688524590</v>
+        <v>32.142857142857</v>
       </c>
       <c r="F21" s="17">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="G21" s="17">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="H21" s="18">
-        <v>-21.111111111111</v>
+        <v>-11.450381679389</v>
       </c>
       <c r="I21" s="17">
-        <v>521</v>
+        <v>597</v>
       </c>
       <c r="J21" s="17">
-        <v>604</v>
+        <v>660</v>
       </c>
       <c r="K21" s="18">
-        <v>-13.741721854304</v>
+        <v>-9.545454545454</v>
       </c>
       <c r="L21" s="18">
-        <v>-18.466353677621</v>
+        <v>-14.714285714285</v>
       </c>
       <c r="M21" s="18">
-        <v>10.615711252653</v>
+        <v>16.6015625</v>
       </c>
       <c r="N21" s="18">
-        <v>-77.377333912288</v>
+        <v>-76.186677303550</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="14">
+        <v>1</v>
       </c>
       <c r="D23" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E23" s="15">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="F23" s="14">
         <v>9</v>
       </c>
       <c r="G23" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H23" s="15">
-        <v>-30.769230769230</v>
+        <v>-25</v>
       </c>
       <c r="I23" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J23" s="14">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K23" s="15">
-        <v>-9.523809523809</v>
+        <v>-20</v>
       </c>
       <c r="L23" s="15">
-        <v>72.727272727272</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M23" s="15">
-        <v>171.428571428571</v>
+        <v>150</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D24" s="14">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E24" s="15">
-        <v>-7.8125</v>
+        <v>-4.761904761904</v>
       </c>
       <c r="F24" s="14">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="G24" s="14">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="H24" s="15">
-        <v>-34.267912772585</v>
+        <v>-30.194805194805</v>
       </c>
       <c r="I24" s="14">
-        <v>523</v>
+        <v>584</v>
       </c>
       <c r="J24" s="14">
-        <v>809</v>
+        <v>872</v>
       </c>
       <c r="K24" s="15">
-        <v>-35.352286773794</v>
+        <v>-33.027522935779</v>
       </c>
       <c r="L24" s="15">
-        <v>-35.985312117503</v>
+        <v>-35.964912280701</v>
       </c>
       <c r="M24" s="15">
-        <v>-10.902896081771</v>
+        <v>-9.457364341085</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D25" s="14">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E25" s="15">
-        <v>-24.242424242424</v>
+        <v>-6.451612903225</v>
       </c>
       <c r="F25" s="14">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G25" s="14">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="H25" s="15">
-        <v>-44.198895027624</v>
+        <v>-37.575757575757</v>
       </c>
       <c r="I25" s="14">
-        <v>262</v>
+        <v>291</v>
       </c>
       <c r="J25" s="14">
-        <v>485</v>
+        <v>516</v>
       </c>
       <c r="K25" s="15">
-        <v>-45.979381443299</v>
+        <v>-43.604651162790</v>
       </c>
       <c r="L25" s="15">
-        <v>-41.906873614190</v>
+        <v>-43.1640625</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D26" s="14">
         <v>42</v>
       </c>
       <c r="E26" s="15">
-        <v>-30.952380952381</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="G26" s="14">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="H26" s="15">
-        <v>10.9375</v>
+        <v>-2.142857142857</v>
       </c>
       <c r="I26" s="14">
-        <v>281</v>
+        <v>315</v>
       </c>
       <c r="J26" s="14">
-        <v>310</v>
+        <v>352</v>
       </c>
       <c r="K26" s="15">
-        <v>-9.354838709677</v>
+        <v>-10.511363636363</v>
       </c>
       <c r="L26" s="15">
-        <v>-6.644518272425</v>
+        <v>-6.804733727810</v>
       </c>
       <c r="M26" s="15">
-        <v>-7.868852459016</v>
+        <v>-9.482758620689</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="15">
-        <v>500</v>
+        <v>-50</v>
       </c>
       <c r="F27" s="14">
+        <v>9</v>
+      </c>
+      <c r="G27" s="14">
+        <v>7</v>
+      </c>
+      <c r="H27" s="15">
+        <v>28.571428571428</v>
+      </c>
+      <c r="I27" s="14">
+        <v>31</v>
+      </c>
+      <c r="J27" s="14">
         <v>16</v>
       </c>
-      <c r="G27" s="14">
-        <v>5</v>
-      </c>
-      <c r="H27" s="15">
-        <v>220</v>
-      </c>
-      <c r="I27" s="14">
-        <v>30</v>
-      </c>
-      <c r="J27" s="14">
-        <v>14</v>
-      </c>
       <c r="K27" s="15">
-        <v>114.285714285714</v>
+        <v>93.75</v>
       </c>
       <c r="L27" s="15">
-        <v>36.363636363636</v>
+        <v>29.166666666666</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,31 +1429,31 @@
         <v>4</v>
       </c>
       <c r="D28" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>33.333333333333</v>
+        <v>300</v>
       </c>
       <c r="F28" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G28" s="14">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H28" s="15">
-        <v>-4.761904761904</v>
+        <v>46.666666666666</v>
       </c>
       <c r="I28" s="14">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J28" s="14">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K28" s="15">
-        <v>-18.604651162790</v>
+        <v>-11.363636363636</v>
       </c>
       <c r="L28" s="15">
-        <v>12.903225806451</v>
+        <v>8.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1467,7 +1467,7 @@
         <v>36</v>
       </c>
       <c r="C29" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1476,31 +1476,31 @@
         <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>2</v>
-      </c>
-      <c r="G29" s="14">
-        <v>1</v>
-      </c>
-      <c r="H29" s="15">
-        <v>100</v>
+        <v>3</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J29" s="14">
         <v>1</v>
       </c>
       <c r="K29" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L29" s="15">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="M29" s="15">
-        <v>-60</v>
+        <v>-40</v>
       </c>
       <c r="N29" s="15">
-        <v>-87.5</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1508,7 +1508,7 @@
         <v>37</v>
       </c>
       <c r="C30" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1517,63 +1517,63 @@
         <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>2</v>
-      </c>
-      <c r="G30" s="14">
-        <v>1</v>
-      </c>
-      <c r="H30" s="15">
-        <v>100</v>
+        <v>3</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J30" s="14">
         <v>1</v>
       </c>
       <c r="K30" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L30" s="15">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="M30" s="15">
-        <v>-60</v>
+        <v>-40</v>
       </c>
       <c r="N30" s="15">
-        <v>-85.714285714285</v>
+        <v>-81.25</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
+      <c r="C31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="14">
         <v>1</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="14">
+        <v>1</v>
+      </c>
+      <c r="G31" s="14">
         <v>2</v>
       </c>
-      <c r="G31" s="14">
-        <v>1</v>
-      </c>
       <c r="H31" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="I31" s="14">
         <v>2</v>
       </c>
       <c r="J31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K31" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L31" s="15">
         <v>-60</v>
@@ -1610,11 +1610,11 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="14">
-        <v>1</v>
-      </c>
-      <c r="E33" s="15">
-        <v>-100</v>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1635,7 +1635,7 @@
         <v>50</v>
       </c>
       <c r="L33" s="15">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-pbsi.xlsx
+++ b/data/source/weekly/cs-en-us-pbsi.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E15" s="15">
-        <v>-100</v>
+        <v>-80</v>
       </c>
       <c r="F15" s="14">
         <v>7</v>
       </c>
       <c r="G15" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H15" s="15">
-        <v>40</v>
+        <v>-12.5</v>
       </c>
       <c r="I15" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J15" s="14">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K15" s="15">
-        <v>109.090909090909</v>
+        <v>50</v>
       </c>
       <c r="L15" s="15">
-        <v>91.666666666666</v>
+        <v>71.428571428571</v>
       </c>
       <c r="M15" s="15">
-        <v>109.090909090909</v>
+        <v>118.181818181818</v>
       </c>
       <c r="N15" s="15">
-        <v>9.523809523809</v>
+        <v>9.090909090909</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
         <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G16" s="14">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H16" s="15">
-        <v>-10.526315789473</v>
+        <v>-12.5</v>
       </c>
       <c r="I16" s="14">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J16" s="14">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K16" s="15">
-        <v>-13.793103448275</v>
+        <v>-14.754098360655</v>
       </c>
       <c r="L16" s="15">
-        <v>-3.846153846153</v>
+        <v>-10.344827586206</v>
       </c>
       <c r="M16" s="15">
-        <v>-23.076923076923</v>
+        <v>-26.760563380281</v>
       </c>
       <c r="N16" s="15">
-        <v>-84.076433121019</v>
+        <v>-84.194528875379</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D17" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E17" s="15">
-        <v>38.095238095238</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G17" s="14">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H17" s="15">
-        <v>-4.938271604938</v>
+        <v>-3.370786516853</v>
       </c>
       <c r="I17" s="14">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="J17" s="14">
-        <v>182</v>
+        <v>206</v>
       </c>
       <c r="K17" s="15">
-        <v>-1.648351648351</v>
+        <v>-1.941747572815</v>
       </c>
       <c r="L17" s="15">
-        <v>-12.682926829268</v>
+        <v>-14.042553191489</v>
       </c>
       <c r="M17" s="15">
-        <v>75.490196078431</v>
+        <v>71.186440677966</v>
       </c>
       <c r="N17" s="15">
-        <v>-11.822660098522</v>
+        <v>-8.597285067873</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>-25</v>
+        <v>20</v>
       </c>
       <c r="F18" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G18" s="14">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H18" s="15">
-        <v>-58.064516129032</v>
+        <v>-44</v>
       </c>
       <c r="I18" s="14">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J18" s="14">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="K18" s="15">
-        <v>-60.824742268041</v>
+        <v>-56.862745098039</v>
       </c>
       <c r="L18" s="15">
-        <v>-28.301886792452</v>
+        <v>-22.807017543859</v>
       </c>
       <c r="M18" s="15">
-        <v>-61.616161616161</v>
+        <v>-58.490566037735</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.259818731117</v>
+        <v>-93.846153846153</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D19" s="14">
+        <v>20</v>
+      </c>
+      <c r="E19" s="15">
         <v>25</v>
-      </c>
-      <c r="E19" s="15">
-        <v>28</v>
       </c>
       <c r="F19" s="14">
         <v>106</v>
       </c>
       <c r="G19" s="14">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="H19" s="15">
-        <v>-5.357142857142</v>
+        <v>1.923076923076</v>
       </c>
       <c r="I19" s="14">
-        <v>268</v>
+        <v>295</v>
       </c>
       <c r="J19" s="14">
-        <v>265</v>
+        <v>285</v>
       </c>
       <c r="K19" s="15">
-        <v>1.132075471698</v>
+        <v>3.508771929824</v>
       </c>
       <c r="L19" s="15">
-        <v>-19.033232628398</v>
+        <v>-17.827298050139</v>
       </c>
       <c r="M19" s="15">
-        <v>54.913294797687</v>
+        <v>56.084656084656</v>
       </c>
       <c r="N19" s="15">
-        <v>-8.843537414965</v>
+        <v>-8.668730650154</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="F20" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G20" s="14">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H20" s="15">
-        <v>-14.285714285714</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I20" s="14">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="J20" s="14">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K20" s="15">
-        <v>-15.217391304347</v>
+        <v>-8.510638297872</v>
       </c>
       <c r="L20" s="15">
-        <v>-15.217391304347</v>
+        <v>-15.686274509803</v>
       </c>
       <c r="M20" s="15">
-        <v>-35</v>
+        <v>-34.848484848484</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.130952380952</v>
+        <v>-96.087352138307</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="D21" s="17">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E21" s="18">
-        <v>32.142857142857</v>
+        <v>3.448275862068</v>
       </c>
       <c r="F21" s="17">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="G21" s="17">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="H21" s="18">
-        <v>-11.450381679389</v>
+        <v>-3.585657370517</v>
       </c>
       <c r="I21" s="17">
-        <v>597</v>
+        <v>660</v>
       </c>
       <c r="J21" s="17">
-        <v>660</v>
+        <v>718</v>
       </c>
       <c r="K21" s="18">
-        <v>-9.545454545454</v>
+        <v>-8.077994428969</v>
       </c>
       <c r="L21" s="18">
-        <v>-14.714285714285</v>
+        <v>-14.838709677419</v>
       </c>
       <c r="M21" s="18">
-        <v>16.6015625</v>
+        <v>17.229129662522</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.186677303550</v>
+        <v>-75.690607734806</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D23" s="14">
+        <v>5</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-40</v>
+      </c>
+      <c r="F23" s="14">
         <v>4</v>
       </c>
-      <c r="E23" s="15">
-        <v>-75</v>
-      </c>
-      <c r="F23" s="14">
-        <v>9</v>
-      </c>
       <c r="G23" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H23" s="15">
-        <v>-25</v>
+        <v>-73.333333333333</v>
       </c>
       <c r="I23" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J23" s="14">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K23" s="15">
-        <v>-20</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="L23" s="15">
-        <v>66.666666666666</v>
+        <v>22.222222222222</v>
       </c>
       <c r="M23" s="15">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D24" s="14">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="E24" s="15">
-        <v>-4.761904761904</v>
+        <v>-37.209302325581</v>
       </c>
       <c r="F24" s="14">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="G24" s="14">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="H24" s="15">
-        <v>-30.194805194805</v>
+        <v>-30.491803278688</v>
       </c>
       <c r="I24" s="14">
-        <v>584</v>
+        <v>636</v>
       </c>
       <c r="J24" s="14">
-        <v>872</v>
+        <v>958</v>
       </c>
       <c r="K24" s="15">
-        <v>-33.027522935779</v>
+        <v>-33.611691022964</v>
       </c>
       <c r="L24" s="15">
-        <v>-35.964912280701</v>
+        <v>-36.526946107784</v>
       </c>
       <c r="M24" s="15">
-        <v>-9.457364341085</v>
+        <v>-10.548523206751</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>29</v>
       </c>
       <c r="D25" s="14">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="E25" s="15">
-        <v>-6.451612903225</v>
+        <v>-47.272727272727</v>
       </c>
       <c r="F25" s="14">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="G25" s="14">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="H25" s="15">
-        <v>-37.575757575757</v>
+        <v>-37.426900584795</v>
       </c>
       <c r="I25" s="14">
-        <v>291</v>
+        <v>321</v>
       </c>
       <c r="J25" s="14">
-        <v>516</v>
+        <v>571</v>
       </c>
       <c r="K25" s="15">
-        <v>-43.604651162790</v>
+        <v>-43.782837127845</v>
       </c>
       <c r="L25" s="15">
-        <v>-43.1640625</v>
+        <v>-43.185840707964</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D26" s="14">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="E26" s="15">
-        <v>-16.666666666666</v>
+        <v>3.571428571428</v>
       </c>
       <c r="F26" s="14">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="G26" s="14">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H26" s="15">
-        <v>-2.142857142857</v>
+        <v>-11.971830985915</v>
       </c>
       <c r="I26" s="14">
-        <v>315</v>
+        <v>345</v>
       </c>
       <c r="J26" s="14">
-        <v>352</v>
+        <v>380</v>
       </c>
       <c r="K26" s="15">
-        <v>-10.511363636363</v>
+        <v>-9.210526315789</v>
       </c>
       <c r="L26" s="15">
-        <v>-6.804733727810</v>
+        <v>-7.008086253369</v>
       </c>
       <c r="M26" s="15">
-        <v>-9.482758620689</v>
+        <v>-12.658227848101</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,31 +1388,31 @@
         <v>1</v>
       </c>
       <c r="D27" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E27" s="15">
-        <v>-50</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="F27" s="14">
         <v>9</v>
       </c>
       <c r="G27" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H27" s="15">
-        <v>28.571428571428</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="I27" s="14">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J27" s="14">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="K27" s="15">
-        <v>93.75</v>
+        <v>45.454545454545</v>
       </c>
       <c r="L27" s="15">
-        <v>29.166666666666</v>
+        <v>23.076923076923</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E28" s="15">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G28" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H28" s="15">
-        <v>46.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J28" s="14">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K28" s="15">
-        <v>-11.363636363636</v>
+        <v>-10.204081632653</v>
       </c>
       <c r="L28" s="15">
-        <v>8.333333333333</v>
+        <v>15.789473684210</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,38 +1466,38 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
+      <c r="C29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="14">
         <v>1</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
         <v>3</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15">
+        <v>200</v>
       </c>
       <c r="I29" s="14">
         <v>3</v>
       </c>
       <c r="J29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K29" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="L29" s="15">
-        <v>-25</v>
+        <v>-40</v>
       </c>
       <c r="M29" s="15">
-        <v>-40</v>
+        <v>-62.5</v>
       </c>
       <c r="N29" s="15">
         <v>-83.333333333333</v>
@@ -1507,38 +1507,38 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
+      <c r="C30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="14">
         <v>1</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="14">
         <v>3</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>200</v>
       </c>
       <c r="I30" s="14">
         <v>3</v>
       </c>
       <c r="J30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K30" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="L30" s="15">
-        <v>-25</v>
+        <v>-40</v>
       </c>
       <c r="M30" s="15">
-        <v>-40</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="N30" s="15">
         <v>-81.25</v>
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="14">
         <v>1</v>
@@ -1576,7 +1576,7 @@
         <v>0</v>
       </c>
       <c r="L31" s="15">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-pbsi.xlsx
+++ b/data/source/weekly/cs-en-us-pbsi.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -202,25 +202,25 @@
     <t>0</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
+    <t>Robbery</t>
+  </si>
+  <si>
+    <t>Fel. Assault</t>
+  </si>
+  <si>
+    <t>Burglary</t>
+  </si>
+  <si>
+    <t>Gr. Larceny</t>
+  </si>
+  <si>
+    <t>G.L.A.</t>
+  </si>
+  <si>
     <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
-  </si>
-  <si>
-    <t>Robbery</t>
-  </si>
-  <si>
-    <t>Fel. Assault</t>
-  </si>
-  <si>
-    <t>Burglary</t>
-  </si>
-  <si>
-    <t>Gr. Larceny</t>
-  </si>
-  <si>
-    <t>G.L.A.</t>
   </si>
   <si>
     <t>TOTAL</t>
@@ -854,26 +854,26 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15">
+        <v>-100</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>20</v>
       </c>
       <c r="J14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" s="15">
         <v>-100</v>
@@ -890,248 +890,248 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="14">
         <v>1</v>
       </c>
       <c r="D15" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E15" s="15">
-        <v>-80</v>
+        <v>0</v>
       </c>
       <c r="F15" s="14">
+        <v>8</v>
+      </c>
+      <c r="G15" s="14">
         <v>7</v>
       </c>
-      <c r="G15" s="14">
-        <v>8</v>
-      </c>
       <c r="H15" s="15">
-        <v>-12.5</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I15" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J15" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K15" s="15">
-        <v>50</v>
+        <v>52.941176470588</v>
       </c>
       <c r="L15" s="15">
-        <v>71.428571428571</v>
+        <v>73.333333333333</v>
       </c>
       <c r="M15" s="15">
-        <v>118.181818181818</v>
+        <v>136.363636363636</v>
       </c>
       <c r="N15" s="15">
-        <v>9.090909090909</v>
+        <v>8.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
         <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>-33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F16" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G16" s="14">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H16" s="15">
-        <v>-12.5</v>
+        <v>30.769230769230</v>
       </c>
       <c r="I16" s="14">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="J16" s="14">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="K16" s="15">
-        <v>-14.754098360655</v>
+        <v>-10.9375</v>
       </c>
       <c r="L16" s="15">
-        <v>-10.344827586206</v>
+        <v>-21.917808219178</v>
       </c>
       <c r="M16" s="15">
-        <v>-26.760563380281</v>
+        <v>-32.941176470588</v>
       </c>
       <c r="N16" s="15">
-        <v>-84.194528875379</v>
+        <v>-83.478260869565</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" s="14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D17" s="14">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E17" s="15">
-        <v>-8.333333333333</v>
+        <v>23.529411764705</v>
       </c>
       <c r="F17" s="14">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G17" s="14">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="H17" s="15">
-        <v>-3.370786516853</v>
+        <v>7.228915662650</v>
       </c>
       <c r="I17" s="14">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="J17" s="14">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="K17" s="15">
-        <v>-1.941747572815</v>
+        <v>0.896860986547</v>
       </c>
       <c r="L17" s="15">
-        <v>-14.042553191489</v>
+        <v>-8.906882591093</v>
       </c>
       <c r="M17" s="15">
-        <v>71.186440677966</v>
+        <v>82.926829268292</v>
       </c>
       <c r="N17" s="15">
-        <v>-8.597285067873</v>
+        <v>-5.462184873949</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C18" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D18" s="14">
         <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F18" s="14">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G18" s="14">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H18" s="15">
-        <v>-44</v>
+        <v>-4.545454545454</v>
       </c>
       <c r="I18" s="14">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J18" s="14">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="K18" s="15">
-        <v>-56.862745098039</v>
+        <v>-52.336448598130</v>
       </c>
       <c r="L18" s="15">
-        <v>-22.807017543859</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="M18" s="15">
-        <v>-58.490566037735</v>
+        <v>-57.5</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.846153846153</v>
+        <v>-93.527918781725</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" s="14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D19" s="14">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E19" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="G19" s="14">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H19" s="15">
-        <v>1.923076923076</v>
+        <v>15.306122448979</v>
       </c>
       <c r="I19" s="14">
-        <v>295</v>
+        <v>322</v>
       </c>
       <c r="J19" s="14">
-        <v>285</v>
+        <v>313</v>
       </c>
       <c r="K19" s="15">
-        <v>3.508771929824</v>
+        <v>2.875399361022</v>
       </c>
       <c r="L19" s="15">
-        <v>-17.827298050139</v>
+        <v>-18.066157760814</v>
       </c>
       <c r="M19" s="15">
-        <v>56.084656084656</v>
+        <v>57.073170731707</v>
       </c>
       <c r="N19" s="15">
-        <v>-8.668730650154</v>
+        <v>-9.039548022598</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" s="14">
+        <v>6</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>4</v>
-      </c>
-      <c r="D20" s="14">
-        <v>1</v>
-      </c>
-      <c r="E20" s="15">
-        <v>300</v>
-      </c>
       <c r="F20" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G20" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H20" s="15">
-        <v>66.666666666666</v>
+        <v>166.666666666667</v>
       </c>
       <c r="I20" s="14">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="J20" s="14">
         <v>47</v>
       </c>
       <c r="K20" s="15">
-        <v>-8.510638297872</v>
+        <v>2.127659574468</v>
       </c>
       <c r="L20" s="15">
-        <v>-15.686274509803</v>
+        <v>-12.727272727272</v>
       </c>
       <c r="M20" s="15">
-        <v>-34.848484848484</v>
+        <v>-30.434782608695</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.087352138307</v>
+        <v>-95.973154362416</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D21" s="17">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E21" s="18">
-        <v>3.448275862068</v>
+        <v>23.636363636363</v>
       </c>
       <c r="F21" s="17">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="G21" s="17">
-        <v>251</v>
+        <v>230</v>
       </c>
       <c r="H21" s="18">
-        <v>-3.585657370517</v>
+        <v>14.782608695652</v>
       </c>
       <c r="I21" s="17">
-        <v>660</v>
+        <v>729</v>
       </c>
       <c r="J21" s="17">
-        <v>718</v>
+        <v>773</v>
       </c>
       <c r="K21" s="18">
-        <v>-8.077994428969</v>
+        <v>-5.692108667529</v>
       </c>
       <c r="L21" s="18">
-        <v>-14.838709677419</v>
+        <v>-13.931523022432</v>
       </c>
       <c r="M21" s="18">
-        <v>17.229129662522</v>
+        <v>18.536585365853</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.690607734806</v>
+        <v>-75.262979300984</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1186,7 +1186,7 @@
         <v>20</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
@@ -1195,7 +1195,7 @@
         <v>20</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I22" s="13" t="s">
         <v>20</v>
@@ -1204,16 +1204,16 @@
         <v>20</v>
       </c>
       <c r="K22" s="13" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="L22" s="13" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="M22" s="13" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1224,37 +1224,37 @@
         <v>3</v>
       </c>
       <c r="D23" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E23" s="15">
-        <v>-40</v>
+        <v>50</v>
       </c>
       <c r="F23" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G23" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H23" s="15">
-        <v>-73.333333333333</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="I23" s="14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J23" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K23" s="15">
-        <v>-26.666666666666</v>
+        <v>-21.875</v>
       </c>
       <c r="L23" s="15">
-        <v>22.222222222222</v>
+        <v>4.166666666666</v>
       </c>
       <c r="M23" s="15">
-        <v>120</v>
+        <v>127.272727272727</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D24" s="14">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E24" s="15">
-        <v>-37.209302325581</v>
+        <v>-22.352941176470</v>
       </c>
       <c r="F24" s="14">
-        <v>212</v>
+        <v>239</v>
       </c>
       <c r="G24" s="14">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="H24" s="15">
-        <v>-30.491803278688</v>
+        <v>-19.798657718120</v>
       </c>
       <c r="I24" s="14">
-        <v>636</v>
+        <v>702</v>
       </c>
       <c r="J24" s="14">
-        <v>958</v>
+        <v>1043</v>
       </c>
       <c r="K24" s="15">
-        <v>-33.611691022964</v>
+        <v>-32.694151486097</v>
       </c>
       <c r="L24" s="15">
-        <v>-36.526946107784</v>
+        <v>-35.477941176470</v>
       </c>
       <c r="M24" s="15">
-        <v>-10.548523206751</v>
+        <v>-8.355091383812</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D25" s="14">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E25" s="15">
-        <v>-47.272727272727</v>
+        <v>-41.509433962264</v>
       </c>
       <c r="F25" s="14">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="G25" s="14">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H25" s="15">
-        <v>-37.426900584795</v>
+        <v>-32.558139534883</v>
       </c>
       <c r="I25" s="14">
-        <v>321</v>
+        <v>352</v>
       </c>
       <c r="J25" s="14">
-        <v>571</v>
+        <v>624</v>
       </c>
       <c r="K25" s="15">
-        <v>-43.782837127845</v>
+        <v>-43.589743589743</v>
       </c>
       <c r="L25" s="15">
-        <v>-43.185840707964</v>
+        <v>-43.042071197411</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1347,37 +1347,37 @@
         <v>29</v>
       </c>
       <c r="D26" s="14">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E26" s="15">
-        <v>3.571428571428</v>
+        <v>-30.952380952381</v>
       </c>
       <c r="F26" s="14">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G26" s="14">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="H26" s="15">
-        <v>-11.971830985915</v>
+        <v>-20.129870129870</v>
       </c>
       <c r="I26" s="14">
-        <v>345</v>
+        <v>376</v>
       </c>
       <c r="J26" s="14">
-        <v>380</v>
+        <v>422</v>
       </c>
       <c r="K26" s="15">
-        <v>-9.210526315789</v>
+        <v>-10.900473933649</v>
       </c>
       <c r="L26" s="15">
-        <v>-7.008086253369</v>
+        <v>-6.930693069306</v>
       </c>
       <c r="M26" s="15">
-        <v>-12.658227848101</v>
+        <v>-12.354312354312</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1385,40 +1385,40 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D27" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E27" s="15">
-        <v>-83.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G27" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H27" s="15">
-        <v>-18.181818181818</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J27" s="14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K27" s="15">
-        <v>45.454545454545</v>
+        <v>44</v>
       </c>
       <c r="L27" s="15">
-        <v>23.076923076923</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,40 +1426,40 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D28" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F28" s="14">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G28" s="14">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>8.333333333333</v>
       </c>
       <c r="I28" s="14">
         <v>44</v>
       </c>
       <c r="J28" s="14">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K28" s="15">
-        <v>-10.204081632653</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="L28" s="15">
-        <v>15.789473684210</v>
+        <v>4.761904761904</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1479,28 +1479,28 @@
         <v>3</v>
       </c>
       <c r="G29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="I29" s="14">
         <v>3</v>
       </c>
       <c r="J29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K29" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L29" s="15">
         <v>-40</v>
       </c>
       <c r="M29" s="15">
-        <v>-62.5</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N29" s="15">
-        <v>-83.333333333333</v>
+        <v>-84.210526315789</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1520,28 +1520,28 @@
         <v>3</v>
       </c>
       <c r="G30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="I30" s="14">
         <v>3</v>
       </c>
       <c r="J30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K30" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L30" s="15">
         <v>-40</v>
       </c>
       <c r="M30" s="15">
-        <v>-57.142857142857</v>
+        <v>-62.5</v>
       </c>
       <c r="N30" s="15">
-        <v>-81.25</v>
+        <v>-82.352941176470</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,34 +1555,34 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F31" s="14">
+        <v>2</v>
+      </c>
+      <c r="G31" s="14">
         <v>1</v>
       </c>
-      <c r="G31" s="14">
-        <v>2</v>
-      </c>
       <c r="H31" s="15">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="I31" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J31" s="14">
         <v>2</v>
       </c>
       <c r="K31" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L31" s="15">
-        <v>-66.666666666666</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1638,10 +1638,10 @@
         <v>0</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>80</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C41" s="14">
         <v>1035</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C42" s="14">
         <v>1225</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C43" s="14">
         <v>3641</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C44" s="14">
         <v>2075</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C45" s="14">
         <v>7224</v>

--- a/data/source/weekly/cs-en-us-pbsi.xlsx
+++ b/data/source/weekly/cs-en-us-pbsi.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -202,6 +202,9 @@
     <t>0</t>
   </si>
   <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
   </si>
   <si>
@@ -218,9 +221,6 @@
   </si>
   <si>
     <t>G.L.A.</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>TOTAL</t>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -890,7 +890,7 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" s="14">
         <v>1</v>
@@ -902,236 +902,236 @@
         <v>0</v>
       </c>
       <c r="F15" s="14">
+        <v>4</v>
+      </c>
+      <c r="G15" s="14">
         <v>8</v>
       </c>
-      <c r="G15" s="14">
-        <v>7</v>
-      </c>
       <c r="H15" s="15">
-        <v>14.285714285714</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J15" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K15" s="15">
-        <v>52.941176470588</v>
+        <v>50</v>
       </c>
       <c r="L15" s="15">
-        <v>73.333333333333</v>
+        <v>68.75</v>
       </c>
       <c r="M15" s="15">
-        <v>136.363636363636</v>
+        <v>145.454545454545</v>
       </c>
       <c r="N15" s="15">
-        <v>8.333333333333</v>
+        <v>-3.571428571428</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G16" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H16" s="15">
-        <v>30.769230769230</v>
+        <v>36.363636363636</v>
       </c>
       <c r="I16" s="14">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J16" s="14">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K16" s="15">
-        <v>-10.9375</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="L16" s="15">
-        <v>-21.917808219178</v>
+        <v>-27.710843373494</v>
       </c>
       <c r="M16" s="15">
-        <v>-32.941176470588</v>
+        <v>-34.065934065934</v>
       </c>
       <c r="N16" s="15">
-        <v>-83.478260869565</v>
+        <v>-83.471074380165</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" s="14">
         <v>21</v>
       </c>
       <c r="D17" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E17" s="15">
-        <v>23.529411764705</v>
+        <v>5</v>
       </c>
       <c r="F17" s="14">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G17" s="14">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H17" s="15">
-        <v>7.228915662650</v>
+        <v>15.853658536585</v>
       </c>
       <c r="I17" s="14">
-        <v>225</v>
+        <v>247</v>
       </c>
       <c r="J17" s="14">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="K17" s="15">
-        <v>0.896860986547</v>
+        <v>1.646090534979</v>
       </c>
       <c r="L17" s="15">
-        <v>-8.906882591093</v>
+        <v>-7.490636704119</v>
       </c>
       <c r="M17" s="15">
-        <v>82.926829268292</v>
+        <v>82.962962962963</v>
       </c>
       <c r="N17" s="15">
-        <v>-5.462184873949</v>
+        <v>-5.363984674329</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E18" s="15">
-        <v>40</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F18" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G18" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H18" s="15">
-        <v>-4.545454545454</v>
+        <v>-4.347826086956</v>
       </c>
       <c r="I18" s="14">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="J18" s="14">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="K18" s="15">
-        <v>-52.336448598130</v>
+        <v>-50.862068965517</v>
       </c>
       <c r="L18" s="15">
-        <v>-19.047619047619</v>
+        <v>-16.176470588235</v>
       </c>
       <c r="M18" s="15">
-        <v>-57.5</v>
+        <v>-57.462686567164</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.527918781725</v>
+        <v>-93.395133256083</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="14">
         <v>25</v>
-      </c>
-      <c r="C19" s="14">
-        <v>28</v>
       </c>
       <c r="D19" s="14">
         <v>28</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>-10.714285714285</v>
       </c>
       <c r="F19" s="14">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="G19" s="14">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H19" s="15">
-        <v>15.306122448979</v>
+        <v>5.940594059405</v>
       </c>
       <c r="I19" s="14">
-        <v>322</v>
+        <v>345</v>
       </c>
       <c r="J19" s="14">
-        <v>313</v>
+        <v>341</v>
       </c>
       <c r="K19" s="15">
-        <v>2.875399361022</v>
+        <v>1.173020527859</v>
       </c>
       <c r="L19" s="15">
-        <v>-18.066157760814</v>
+        <v>-17.067307692307</v>
       </c>
       <c r="M19" s="15">
-        <v>57.073170731707</v>
+        <v>53.333333333333</v>
       </c>
       <c r="N19" s="15">
-        <v>-9.039548022598</v>
+        <v>-10.852713178294</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="14">
+        <v>13</v>
+      </c>
+      <c r="D20" s="14">
+        <v>5</v>
+      </c>
+      <c r="E20" s="15">
+        <v>160</v>
+      </c>
+      <c r="F20" s="14">
         <v>26</v>
       </c>
-      <c r="C20" s="14">
-        <v>6</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="F20" s="14">
-        <v>16</v>
-      </c>
       <c r="G20" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H20" s="15">
-        <v>166.666666666667</v>
+        <v>225</v>
       </c>
       <c r="I20" s="14">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="J20" s="14">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="K20" s="15">
-        <v>2.127659574468</v>
+        <v>15.384615384615</v>
       </c>
       <c r="L20" s="15">
-        <v>-12.727272727272</v>
+        <v>-1.639344262295</v>
       </c>
       <c r="M20" s="15">
-        <v>-30.434782608695</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.973154362416</v>
+        <v>-95.279307631786</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D21" s="17">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E21" s="18">
-        <v>23.636363636363</v>
+        <v>3.076923076923</v>
       </c>
       <c r="F21" s="17">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="G21" s="17">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="H21" s="18">
-        <v>14.782608695652</v>
+        <v>14.957264957265</v>
       </c>
       <c r="I21" s="17">
-        <v>729</v>
+        <v>796</v>
       </c>
       <c r="J21" s="17">
-        <v>773</v>
+        <v>838</v>
       </c>
       <c r="K21" s="18">
-        <v>-5.692108667529</v>
+        <v>-5.011933174224</v>
       </c>
       <c r="L21" s="18">
-        <v>-13.931523022432</v>
+        <v>-12.719298245614</v>
       </c>
       <c r="M21" s="18">
-        <v>18.536585365853</v>
+        <v>19.161676646706</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.262979300984</v>
+        <v>-74.960679458949</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1186,7 +1186,7 @@
         <v>20</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
@@ -1195,7 +1195,7 @@
         <v>20</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I22" s="13" t="s">
         <v>20</v>
@@ -1204,16 +1204,16 @@
         <v>20</v>
       </c>
       <c r="K22" s="13" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="L22" s="13" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="M22" s="13" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D23" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F23" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G23" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H23" s="15">
-        <v>-46.153846153846</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I23" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J23" s="14">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K23" s="15">
-        <v>-21.875</v>
+        <v>-21.212121212121</v>
       </c>
       <c r="L23" s="15">
-        <v>4.166666666666</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="M23" s="15">
-        <v>127.272727272727</v>
+        <v>100</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D24" s="14">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E24" s="15">
-        <v>-22.352941176470</v>
+        <v>-19.753086419753</v>
       </c>
       <c r="F24" s="14">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="G24" s="14">
-        <v>298</v>
+        <v>315</v>
       </c>
       <c r="H24" s="15">
-        <v>-19.798657718120</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I24" s="14">
-        <v>702</v>
+        <v>768</v>
       </c>
       <c r="J24" s="14">
-        <v>1043</v>
+        <v>1124</v>
       </c>
       <c r="K24" s="15">
-        <v>-32.694151486097</v>
+        <v>-31.672597864768</v>
       </c>
       <c r="L24" s="15">
-        <v>-35.477941176470</v>
+        <v>-34.526854219948</v>
       </c>
       <c r="M24" s="15">
-        <v>-8.355091383812</v>
+        <v>-6.909090909090</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D25" s="14">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="E25" s="15">
-        <v>-41.509433962264</v>
+        <v>-45.238095238095</v>
       </c>
       <c r="F25" s="14">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="G25" s="14">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="H25" s="15">
-        <v>-32.558139534883</v>
+        <v>-37.569060773480</v>
       </c>
       <c r="I25" s="14">
-        <v>352</v>
+        <v>375</v>
       </c>
       <c r="J25" s="14">
-        <v>624</v>
+        <v>666</v>
       </c>
       <c r="K25" s="15">
-        <v>-43.589743589743</v>
+        <v>-43.693693693693</v>
       </c>
       <c r="L25" s="15">
-        <v>-43.042071197411</v>
+        <v>-43.181818181818</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="D26" s="14">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E26" s="15">
-        <v>-30.952380952381</v>
+        <v>38.235294117647</v>
       </c>
       <c r="F26" s="14">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="G26" s="14">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="H26" s="15">
-        <v>-20.129870129870</v>
+        <v>-3.424657534246</v>
       </c>
       <c r="I26" s="14">
-        <v>376</v>
+        <v>422</v>
       </c>
       <c r="J26" s="14">
-        <v>422</v>
+        <v>456</v>
       </c>
       <c r="K26" s="15">
-        <v>-10.900473933649</v>
+        <v>-7.456140350877</v>
       </c>
       <c r="L26" s="15">
-        <v>-6.930693069306</v>
+        <v>-2.764976958525</v>
       </c>
       <c r="M26" s="15">
-        <v>-12.354312354312</v>
+        <v>-7.252747252747</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1385,40 +1385,40 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D27" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E27" s="15">
         <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G27" s="14">
         <v>12</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="I27" s="14">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J27" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K27" s="15">
-        <v>44</v>
+        <v>42.307692307692</v>
       </c>
       <c r="L27" s="15">
-        <v>33.333333333333</v>
+        <v>32.142857142857</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,40 +1426,40 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E28" s="15">
-        <v>-66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="F28" s="14">
+        <v>14</v>
+      </c>
+      <c r="G28" s="14">
         <v>13</v>
       </c>
-      <c r="G28" s="14">
-        <v>12</v>
-      </c>
       <c r="H28" s="15">
-        <v>8.333333333333</v>
+        <v>7.692307692307</v>
       </c>
       <c r="I28" s="14">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J28" s="14">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K28" s="15">
-        <v>-15.384615384615</v>
+        <v>-12.5</v>
       </c>
       <c r="L28" s="15">
-        <v>4.761904761904</v>
+        <v>11.363636363636</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1469,20 +1469,20 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="14">
         <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F29" s="14">
-        <v>3</v>
       </c>
       <c r="G29" s="14">
         <v>2</v>
       </c>
       <c r="H29" s="15">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="I29" s="14">
         <v>3</v>
@@ -1497,10 +1497,10 @@
         <v>-40</v>
       </c>
       <c r="M29" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="N29" s="15">
-        <v>-84.210526315789</v>
+        <v>-85</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,20 +1510,20 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="14">
         <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F30" s="14">
-        <v>3</v>
       </c>
       <c r="G30" s="14">
         <v>2</v>
       </c>
       <c r="H30" s="15">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="I30" s="14">
         <v>3</v>
@@ -1538,10 +1538,10 @@
         <v>-40</v>
       </c>
       <c r="M30" s="15">
-        <v>-62.5</v>
+        <v>-70</v>
       </c>
       <c r="N30" s="15">
-        <v>-82.352941176470</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,7 +1555,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F31" s="14">
         <v>2</v>
@@ -1567,22 +1567,22 @@
         <v>100</v>
       </c>
       <c r="I31" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J31" s="14">
         <v>2</v>
       </c>
       <c r="K31" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L31" s="15">
-        <v>-57.142857142857</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,16 +1614,16 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="14">
-        <v>1</v>
-      </c>
-      <c r="H33" s="15">
-        <v>-100</v>
+      <c r="G33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I33" s="14">
         <v>3</v>
@@ -1638,10 +1638,10 @@
         <v>0</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>80</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C41" s="14">
         <v>1035</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C42" s="14">
         <v>1225</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C43" s="14">
         <v>3641</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C44" s="14">
         <v>2075</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C45" s="14">
         <v>7224</v>

--- a/data/source/weekly/cs-en-us-pbsi.xlsx
+++ b/data/source/weekly/cs-en-us-pbsi.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E15" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F15" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G15" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H15" s="15">
-        <v>-50</v>
+        <v>-40</v>
       </c>
       <c r="I15" s="14">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J15" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K15" s="15">
-        <v>50</v>
+        <v>38.095238095238</v>
       </c>
       <c r="L15" s="15">
-        <v>68.75</v>
+        <v>81.25</v>
       </c>
       <c r="M15" s="15">
-        <v>145.454545454545</v>
+        <v>141.666666666667</v>
       </c>
       <c r="N15" s="15">
-        <v>-3.571428571428</v>
+        <v>3.571428571428</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E16" s="15">
         <v>0</v>
       </c>
       <c r="F16" s="14">
+        <v>17</v>
+      </c>
+      <c r="G16" s="14">
         <v>15</v>
       </c>
-      <c r="G16" s="14">
-        <v>11</v>
-      </c>
       <c r="H16" s="15">
-        <v>36.363636363636</v>
+        <v>13.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="J16" s="14">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="K16" s="15">
-        <v>-9.090909090909</v>
+        <v>-6.849315068493</v>
       </c>
       <c r="L16" s="15">
-        <v>-27.710843373494</v>
+        <v>-23.595505617977</v>
       </c>
       <c r="M16" s="15">
-        <v>-34.065934065934</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N16" s="15">
-        <v>-83.471074380165</v>
+        <v>-82.337662337662</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D17" s="14">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E17" s="15">
-        <v>5</v>
+        <v>7.142857142857</v>
       </c>
       <c r="F17" s="14">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="G17" s="14">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H17" s="15">
-        <v>15.853658536585</v>
+        <v>8</v>
       </c>
       <c r="I17" s="14">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="J17" s="14">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="K17" s="15">
-        <v>1.646090534979</v>
+        <v>1.945525291828</v>
       </c>
       <c r="L17" s="15">
-        <v>-7.490636704119</v>
+        <v>-8.391608391608</v>
       </c>
       <c r="M17" s="15">
-        <v>82.962962962963</v>
+        <v>83.216783216783</v>
       </c>
       <c r="N17" s="15">
-        <v>-5.363984674329</v>
+        <v>-10.580204778157</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>-44.444444444444</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F18" s="14">
+        <v>23</v>
+      </c>
+      <c r="G18" s="14">
         <v>22</v>
       </c>
-      <c r="G18" s="14">
-        <v>23</v>
-      </c>
       <c r="H18" s="15">
-        <v>-4.347826086956</v>
+        <v>4.545454545454</v>
       </c>
       <c r="I18" s="14">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="J18" s="14">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="K18" s="15">
-        <v>-50.862068965517</v>
+        <v>-48.739495798319</v>
       </c>
       <c r="L18" s="15">
-        <v>-16.176470588235</v>
+        <v>-14.084507042253</v>
       </c>
       <c r="M18" s="15">
-        <v>-57.462686567164</v>
+        <v>-58.503401360544</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.395133256083</v>
+        <v>-93.311403508771</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D19" s="14">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E19" s="15">
-        <v>-10.714285714285</v>
+        <v>18.181818181818</v>
       </c>
       <c r="F19" s="14">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="G19" s="14">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H19" s="15">
-        <v>5.940594059405</v>
+        <v>2.040816326530</v>
       </c>
       <c r="I19" s="14">
-        <v>345</v>
+        <v>370</v>
       </c>
       <c r="J19" s="14">
-        <v>341</v>
+        <v>363</v>
       </c>
       <c r="K19" s="15">
-        <v>1.173020527859</v>
+        <v>1.928374655647</v>
       </c>
       <c r="L19" s="15">
-        <v>-17.067307692307</v>
+        <v>-15.137614678899</v>
       </c>
       <c r="M19" s="15">
-        <v>53.333333333333</v>
+        <v>48.594377510040</v>
       </c>
       <c r="N19" s="15">
-        <v>-10.852713178294</v>
+        <v>-12.114014251781</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E20" s="15">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G20" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H20" s="15">
-        <v>225</v>
+        <v>150</v>
       </c>
       <c r="I20" s="14">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J20" s="14">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K20" s="15">
-        <v>15.384615384615</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L20" s="15">
-        <v>-1.639344262295</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="M20" s="15">
-        <v>-14.285714285714</v>
+        <v>-17.948717948717</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.279307631786</v>
+        <v>-95.321637426900</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D21" s="17">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="E21" s="18">
-        <v>3.076923076923</v>
+        <v>9.433962264150</v>
       </c>
       <c r="F21" s="17">
-        <v>269</v>
+        <v>252</v>
       </c>
       <c r="G21" s="17">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="H21" s="18">
-        <v>14.957264957265</v>
+        <v>9.090909090909</v>
       </c>
       <c r="I21" s="17">
-        <v>796</v>
+        <v>854</v>
       </c>
       <c r="J21" s="17">
-        <v>838</v>
+        <v>891</v>
       </c>
       <c r="K21" s="18">
-        <v>-5.011933174224</v>
+        <v>-4.152637485970</v>
       </c>
       <c r="L21" s="18">
-        <v>-12.719298245614</v>
+        <v>-11.685625646328</v>
       </c>
       <c r="M21" s="18">
-        <v>19.161676646706</v>
+        <v>16.507503410641</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.960679458949</v>
+        <v>-74.978025197773</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1224,34 +1224,34 @@
         <v>1</v>
       </c>
       <c r="D23" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F23" s="14">
         <v>8</v>
       </c>
       <c r="G23" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H23" s="15">
-        <v>-33.333333333333</v>
+        <v>-20</v>
       </c>
       <c r="I23" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J23" s="14">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K23" s="15">
-        <v>-21.212121212121</v>
+        <v>-22.857142857142</v>
       </c>
       <c r="L23" s="15">
-        <v>-7.142857142857</v>
+        <v>-12.903225806451</v>
       </c>
       <c r="M23" s="15">
-        <v>100</v>
+        <v>92.857142857142</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D24" s="14">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E24" s="15">
-        <v>-19.753086419753</v>
+        <v>-24.705882352941</v>
       </c>
       <c r="F24" s="14">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="G24" s="14">
-        <v>315</v>
+        <v>337</v>
       </c>
       <c r="H24" s="15">
-        <v>-22.222222222222</v>
+        <v>-25.816023738872</v>
       </c>
       <c r="I24" s="14">
-        <v>768</v>
+        <v>831</v>
       </c>
       <c r="J24" s="14">
-        <v>1124</v>
+        <v>1209</v>
       </c>
       <c r="K24" s="15">
-        <v>-31.672597864768</v>
+        <v>-31.265508684863</v>
       </c>
       <c r="L24" s="15">
-        <v>-34.526854219948</v>
+        <v>-33.466773418735</v>
       </c>
       <c r="M24" s="15">
-        <v>-6.909090909090</v>
+        <v>-8.580858085808</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D25" s="14">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E25" s="15">
-        <v>-45.238095238095</v>
+        <v>-31.818181818181</v>
       </c>
       <c r="F25" s="14">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G25" s="14">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="H25" s="15">
-        <v>-37.569060773480</v>
+        <v>-42.268041237113</v>
       </c>
       <c r="I25" s="14">
-        <v>375</v>
+        <v>404</v>
       </c>
       <c r="J25" s="14">
-        <v>666</v>
+        <v>710</v>
       </c>
       <c r="K25" s="15">
-        <v>-43.693693693693</v>
+        <v>-43.098591549295</v>
       </c>
       <c r="L25" s="15">
-        <v>-43.181818181818</v>
+        <v>-42.203147353361</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="D26" s="14">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E26" s="15">
-        <v>38.235294117647</v>
+        <v>-34.285714285714</v>
       </c>
       <c r="F26" s="14">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="G26" s="14">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="H26" s="15">
-        <v>-3.424657534246</v>
+        <v>-7.913669064748</v>
       </c>
       <c r="I26" s="14">
-        <v>422</v>
+        <v>445</v>
       </c>
       <c r="J26" s="14">
-        <v>456</v>
+        <v>491</v>
       </c>
       <c r="K26" s="15">
-        <v>-7.456140350877</v>
+        <v>-9.368635437881</v>
       </c>
       <c r="L26" s="15">
-        <v>-2.764976958525</v>
+        <v>-5.720338983050</v>
       </c>
       <c r="M26" s="15">
-        <v>-7.252747252747</v>
+        <v>-10.282258064516</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E27" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F27" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G27" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H27" s="15">
-        <v>-41.666666666666</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="I27" s="14">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="J27" s="14">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K27" s="15">
-        <v>42.307692307692</v>
+        <v>37.931034482758</v>
       </c>
       <c r="L27" s="15">
-        <v>32.142857142857</v>
+        <v>42.857142857142</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D28" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E28" s="15">
-        <v>25</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F28" s="14">
         <v>14</v>
       </c>
       <c r="G28" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H28" s="15">
-        <v>7.692307692307</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="I28" s="14">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="J28" s="14">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K28" s="15">
-        <v>-12.5</v>
+        <v>-11.864406779661</v>
       </c>
       <c r="L28" s="15">
-        <v>11.363636363636</v>
+        <v>1.960784313725</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1485,30 +1485,30 @@
         <v>-50</v>
       </c>
       <c r="I29" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J29" s="14">
         <v>3</v>
       </c>
       <c r="K29" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L29" s="15">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="M29" s="15">
-        <v>-75</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N29" s="15">
-        <v>-85</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1526,22 +1526,22 @@
         <v>-50</v>
       </c>
       <c r="I30" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J30" s="14">
         <v>3</v>
       </c>
       <c r="K30" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L30" s="15">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="M30" s="15">
-        <v>-70</v>
+        <v>-60</v>
       </c>
       <c r="N30" s="15">
-        <v>-83.333333333333</v>
+        <v>-77.777777777777</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1560,11 +1560,11 @@
       <c r="F31" s="14">
         <v>2</v>
       </c>
-      <c r="G31" s="14">
-        <v>1</v>
-      </c>
-      <c r="H31" s="15">
-        <v>100</v>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I31" s="14">
         <v>4</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="14">
+        <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1616,8 +1616,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>20</v>
+      <c r="F33" s="14">
+        <v>1</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
@@ -1626,16 +1626,16 @@
         <v>21</v>
       </c>
       <c r="I33" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J33" s="14">
         <v>2</v>
       </c>
       <c r="K33" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L33" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-pbsi.xlsx
+++ b/data/source/weekly/cs-en-us-pbsi.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E15" s="15">
-        <v>-33.333333333333</v>
+        <v>200</v>
       </c>
       <c r="F15" s="14">
+        <v>7</v>
+      </c>
+      <c r="G15" s="14">
         <v>6</v>
       </c>
-      <c r="G15" s="14">
-        <v>10</v>
-      </c>
       <c r="H15" s="15">
-        <v>-40</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I15" s="14">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J15" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K15" s="15">
-        <v>38.095238095238</v>
+        <v>45.454545454545</v>
       </c>
       <c r="L15" s="15">
-        <v>81.25</v>
+        <v>77.777777777777</v>
       </c>
       <c r="M15" s="15">
-        <v>141.666666666667</v>
+        <v>88.235294117647</v>
       </c>
       <c r="N15" s="15">
-        <v>3.571428571428</v>
+        <v>14.285714285714</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D16" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
+        <v>100</v>
+      </c>
+      <c r="F16" s="14">
+        <v>24</v>
+      </c>
+      <c r="G16" s="14">
+        <v>16</v>
+      </c>
+      <c r="H16" s="15">
+        <v>50</v>
+      </c>
+      <c r="I16" s="14">
+        <v>77</v>
+      </c>
+      <c r="J16" s="14">
+        <v>77</v>
+      </c>
+      <c r="K16" s="15">
         <v>0</v>
       </c>
-      <c r="F16" s="14">
-        <v>17</v>
-      </c>
-      <c r="G16" s="14">
-        <v>15</v>
-      </c>
-      <c r="H16" s="15">
-        <v>13.333333333333</v>
-      </c>
-      <c r="I16" s="14">
-        <v>68</v>
-      </c>
-      <c r="J16" s="14">
-        <v>73</v>
-      </c>
-      <c r="K16" s="15">
-        <v>-6.849315068493</v>
-      </c>
       <c r="L16" s="15">
-        <v>-23.595505617977</v>
+        <v>-20.618556701030</v>
       </c>
       <c r="M16" s="15">
-        <v>-33.333333333333</v>
+        <v>-31.25</v>
       </c>
       <c r="N16" s="15">
-        <v>-82.337662337662</v>
+        <v>-81.490384615384</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D17" s="14">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E17" s="15">
-        <v>7.142857142857</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
         <v>81</v>
       </c>
       <c r="G17" s="14">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H17" s="15">
-        <v>8</v>
+        <v>9.459459459459</v>
       </c>
       <c r="I17" s="14">
-        <v>262</v>
+        <v>285</v>
       </c>
       <c r="J17" s="14">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="K17" s="15">
-        <v>1.945525291828</v>
+        <v>1.785714285714</v>
       </c>
       <c r="L17" s="15">
-        <v>-8.391608391608</v>
+        <v>-6.25</v>
       </c>
       <c r="M17" s="15">
-        <v>83.216783216783</v>
+        <v>87.5</v>
       </c>
       <c r="N17" s="15">
-        <v>-10.580204778157</v>
+        <v>-8.064516129032</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D18" s="14">
         <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F18" s="14">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G18" s="14">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H18" s="15">
-        <v>4.545454545454</v>
+        <v>5</v>
       </c>
       <c r="I18" s="14">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="J18" s="14">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="K18" s="15">
-        <v>-48.739495798319</v>
+        <v>-45.901639344262</v>
       </c>
       <c r="L18" s="15">
-        <v>-14.084507042253</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="M18" s="15">
-        <v>-58.503401360544</v>
+        <v>-57.419354838709</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.311403508771</v>
+        <v>-93.195876288659</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D19" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E19" s="15">
-        <v>18.181818181818</v>
+        <v>12.5</v>
       </c>
       <c r="F19" s="14">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G19" s="14">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="H19" s="15">
-        <v>2.040816326530</v>
+        <v>0.980392156862</v>
       </c>
       <c r="I19" s="14">
-        <v>370</v>
+        <v>395</v>
       </c>
       <c r="J19" s="14">
-        <v>363</v>
+        <v>387</v>
       </c>
       <c r="K19" s="15">
-        <v>1.928374655647</v>
+        <v>2.067183462532</v>
       </c>
       <c r="L19" s="15">
-        <v>-15.137614678899</v>
+        <v>-13.943355119825</v>
       </c>
       <c r="M19" s="15">
-        <v>48.594377510040</v>
+        <v>48.496240601503</v>
       </c>
       <c r="N19" s="15">
-        <v>-12.114014251781</v>
+        <v>-12.416851441241</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D20" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="F20" s="14">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G20" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H20" s="15">
-        <v>150</v>
+        <v>163.636363636364</v>
       </c>
       <c r="I20" s="14">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="J20" s="14">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K20" s="15">
-        <v>14.285714285714</v>
+        <v>22.413793103448</v>
       </c>
       <c r="L20" s="15">
-        <v>-5.882352941176</v>
+        <v>-6.578947368421</v>
       </c>
       <c r="M20" s="15">
-        <v>-17.948717948717</v>
+        <v>-12.345679012345</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.321637426900</v>
+        <v>-95.143638850889</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="D21" s="17">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E21" s="18">
-        <v>9.433962264150</v>
+        <v>28.070175438596</v>
       </c>
       <c r="F21" s="17">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="G21" s="17">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H21" s="18">
-        <v>9.090909090909</v>
+        <v>15.217391304347</v>
       </c>
       <c r="I21" s="17">
-        <v>854</v>
+        <v>926</v>
       </c>
       <c r="J21" s="17">
-        <v>891</v>
+        <v>948</v>
       </c>
       <c r="K21" s="18">
-        <v>-4.152637485970</v>
+        <v>-2.320675105485</v>
       </c>
       <c r="L21" s="18">
-        <v>-11.685625646328</v>
+        <v>-10.358180058083</v>
       </c>
       <c r="M21" s="18">
-        <v>16.507503410641</v>
+        <v>17.961783439490</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.978025197773</v>
+        <v>-74.588364434687</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D23" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E23" s="15">
-        <v>-50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F23" s="14">
+        <v>9</v>
+      </c>
+      <c r="G23" s="14">
         <v>8</v>
       </c>
-      <c r="G23" s="14">
-        <v>10</v>
-      </c>
       <c r="H23" s="15">
-        <v>-20</v>
+        <v>12.5</v>
       </c>
       <c r="I23" s="14">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J23" s="14">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K23" s="15">
-        <v>-22.857142857142</v>
+        <v>-18.421052631578</v>
       </c>
       <c r="L23" s="15">
-        <v>-12.903225806451</v>
+        <v>-6.060606060606</v>
       </c>
       <c r="M23" s="15">
-        <v>92.857142857142</v>
+        <v>106.666666666667</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D24" s="14">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E24" s="15">
-        <v>-24.705882352941</v>
+        <v>-26.136363636363</v>
       </c>
       <c r="F24" s="14">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="G24" s="14">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="H24" s="15">
-        <v>-25.816023738872</v>
+        <v>-22.713864306784</v>
       </c>
       <c r="I24" s="14">
-        <v>831</v>
+        <v>895</v>
       </c>
       <c r="J24" s="14">
-        <v>1209</v>
+        <v>1297</v>
       </c>
       <c r="K24" s="15">
-        <v>-31.265508684863</v>
+        <v>-30.994602929838</v>
       </c>
       <c r="L24" s="15">
-        <v>-33.466773418735</v>
+        <v>-31.990881458966</v>
       </c>
       <c r="M24" s="15">
-        <v>-8.580858085808</v>
+        <v>-8.766564729867</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D25" s="14">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="E25" s="15">
-        <v>-31.818181818181</v>
+        <v>-57.894736842105</v>
       </c>
       <c r="F25" s="14">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G25" s="14">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H25" s="15">
-        <v>-42.268041237113</v>
+        <v>-44.897959183673</v>
       </c>
       <c r="I25" s="14">
-        <v>404</v>
+        <v>429</v>
       </c>
       <c r="J25" s="14">
-        <v>710</v>
+        <v>767</v>
       </c>
       <c r="K25" s="15">
-        <v>-43.098591549295</v>
+        <v>-44.067796610169</v>
       </c>
       <c r="L25" s="15">
-        <v>-42.203147353361</v>
+        <v>-42.338709677419</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="D26" s="14">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E26" s="15">
-        <v>-34.285714285714</v>
+        <v>-6.818181818181</v>
       </c>
       <c r="F26" s="14">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="G26" s="14">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="H26" s="15">
-        <v>-7.913669064748</v>
+        <v>-9.677419354838</v>
       </c>
       <c r="I26" s="14">
-        <v>445</v>
+        <v>488</v>
       </c>
       <c r="J26" s="14">
-        <v>491</v>
+        <v>535</v>
       </c>
       <c r="K26" s="15">
-        <v>-9.368635437881</v>
+        <v>-8.785046728971</v>
       </c>
       <c r="L26" s="15">
-        <v>-5.720338983050</v>
+        <v>-5.973025048169</v>
       </c>
       <c r="M26" s="15">
-        <v>-10.282258064516</v>
+        <v>-10.622710622710</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D27" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>-33.333333333333</v>
+        <v>200</v>
       </c>
       <c r="F27" s="14">
+        <v>9</v>
+      </c>
+      <c r="G27" s="14">
         <v>8</v>
       </c>
-      <c r="G27" s="14">
-        <v>13</v>
-      </c>
       <c r="H27" s="15">
-        <v>-38.461538461538</v>
+        <v>12.5</v>
       </c>
       <c r="I27" s="14">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J27" s="14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K27" s="15">
-        <v>37.931034482758</v>
+        <v>43.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>42.857142857142</v>
+        <v>34.375</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,31 +1429,31 @@
         <v>4</v>
       </c>
       <c r="D28" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E28" s="15">
-        <v>33.333333333333</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F28" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G28" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H28" s="15">
-        <v>-6.666666666666</v>
+        <v>-6.25</v>
       </c>
       <c r="I28" s="14">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="J28" s="14">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K28" s="15">
-        <v>-11.864406779661</v>
+        <v>-10.769230769230</v>
       </c>
       <c r="L28" s="15">
-        <v>1.960784313725</v>
+        <v>7.407407407407</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1476,31 +1476,31 @@
         <v>21</v>
       </c>
       <c r="F29" s="14">
+        <v>2</v>
+      </c>
+      <c r="G29" s="14">
         <v>1</v>
       </c>
-      <c r="G29" s="14">
-        <v>2</v>
-      </c>
       <c r="H29" s="15">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="I29" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J29" s="14">
         <v>3</v>
       </c>
       <c r="K29" s="15">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L29" s="15">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="M29" s="15">
-        <v>-66.666666666666</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="N29" s="15">
-        <v>-80</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1517,66 +1517,66 @@
         <v>21</v>
       </c>
       <c r="F30" s="14">
+        <v>2</v>
+      </c>
+      <c r="G30" s="14">
         <v>1</v>
       </c>
-      <c r="G30" s="14">
-        <v>2</v>
-      </c>
       <c r="H30" s="15">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="I30" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J30" s="14">
         <v>3</v>
       </c>
       <c r="K30" s="15">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L30" s="15">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="M30" s="15">
-        <v>-60</v>
+        <v>-50</v>
       </c>
       <c r="N30" s="15">
-        <v>-77.777777777777</v>
+        <v>-72.222222222222</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="C31" s="14">
+        <v>1</v>
+      </c>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>0</v>
       </c>
       <c r="F31" s="14">
         <v>2</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="14">
+        <v>1</v>
+      </c>
+      <c r="H31" s="15">
+        <v>100</v>
       </c>
       <c r="I31" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J31" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K31" s="15">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L31" s="15">
-        <v>-42.857142857142</v>
+        <v>-37.5</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
-        <v>1</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-pbsi.xlsx
+++ b/data/source/weekly/cs-en-us-pbsi.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -692,10 +692,10 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -863,11 +863,11 @@
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>-100</v>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>20</v>
@@ -893,81 +893,81 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="14">
         <v>3</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
       <c r="E15" s="15">
-        <v>200</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F15" s="14">
         <v>7</v>
       </c>
       <c r="G15" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H15" s="15">
-        <v>16.666666666666</v>
+        <v>-12.5</v>
       </c>
       <c r="I15" s="14">
+        <v>33</v>
+      </c>
+      <c r="J15" s="14">
+        <v>25</v>
+      </c>
+      <c r="K15" s="15">
         <v>32</v>
       </c>
-      <c r="J15" s="14">
-        <v>22</v>
-      </c>
-      <c r="K15" s="15">
-        <v>45.454545454545</v>
-      </c>
       <c r="L15" s="15">
-        <v>77.777777777777</v>
+        <v>73.684210526315</v>
       </c>
       <c r="M15" s="15">
-        <v>88.235294117647</v>
+        <v>73.684210526315</v>
       </c>
       <c r="N15" s="15">
-        <v>14.285714285714</v>
+        <v>17.857142857142</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>8</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E16" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G16" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H16" s="15">
-        <v>50</v>
+        <v>5.555555555555</v>
       </c>
       <c r="I16" s="14">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J16" s="14">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="K16" s="15">
-        <v>0</v>
+        <v>-4.878048780487</v>
       </c>
       <c r="L16" s="15">
-        <v>-20.618556701030</v>
+        <v>-24.271844660194</v>
       </c>
       <c r="M16" s="15">
-        <v>-31.25</v>
+        <v>-33.898305084745</v>
       </c>
       <c r="N16" s="15">
-        <v>-81.490384615384</v>
+        <v>-82.471910112359</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D17" s="14">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F17" s="14">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G17" s="14">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="H17" s="15">
-        <v>9.459459459459</v>
+        <v>-15.730337078651</v>
       </c>
       <c r="I17" s="14">
-        <v>285</v>
+        <v>302</v>
       </c>
       <c r="J17" s="14">
-        <v>280</v>
+        <v>312</v>
       </c>
       <c r="K17" s="15">
-        <v>1.785714285714</v>
+        <v>-3.205128205128</v>
       </c>
       <c r="L17" s="15">
-        <v>-6.25</v>
+        <v>-6.211180124223</v>
       </c>
       <c r="M17" s="15">
-        <v>87.5</v>
+        <v>83.030303030303</v>
       </c>
       <c r="N17" s="15">
-        <v>-8.064516129032</v>
+        <v>-9.850746268656</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E18" s="15">
-        <v>66.666666666666</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="F18" s="14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G18" s="14">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H18" s="15">
-        <v>5</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I18" s="14">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J18" s="14">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="K18" s="15">
-        <v>-45.901639344262</v>
+        <v>-45.038167938931</v>
       </c>
       <c r="L18" s="15">
-        <v>-15.384615384615</v>
+        <v>-20</v>
       </c>
       <c r="M18" s="15">
-        <v>-57.419354838709</v>
+        <v>-56.363636363636</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.195876288659</v>
+        <v>-93.036750483559</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D19" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E19" s="15">
-        <v>12.5</v>
+        <v>4</v>
       </c>
       <c r="F19" s="14">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G19" s="14">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H19" s="15">
-        <v>0.980392156862</v>
+        <v>3.030303030303</v>
       </c>
       <c r="I19" s="14">
-        <v>395</v>
+        <v>420</v>
       </c>
       <c r="J19" s="14">
-        <v>387</v>
+        <v>412</v>
       </c>
       <c r="K19" s="15">
-        <v>2.067183462532</v>
+        <v>1.941747572815</v>
       </c>
       <c r="L19" s="15">
-        <v>-13.943355119825</v>
+        <v>-13.580246913580</v>
       </c>
       <c r="M19" s="15">
-        <v>48.496240601503</v>
+        <v>49.466192170818</v>
       </c>
       <c r="N19" s="15">
-        <v>-12.416851441241</v>
+        <v>-13.580246913580</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D20" s="14">
         <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>250</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="14">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G20" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H20" s="15">
-        <v>163.636363636364</v>
+        <v>92.307692307692</v>
       </c>
       <c r="I20" s="14">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J20" s="14">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K20" s="15">
-        <v>22.413793103448</v>
+        <v>20</v>
       </c>
       <c r="L20" s="15">
-        <v>-6.578947368421</v>
+        <v>-8.860759493670</v>
       </c>
       <c r="M20" s="15">
-        <v>-12.345679012345</v>
+        <v>-16.279069767441</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.143638850889</v>
+        <v>-95.366795366795</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="D21" s="17">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="E21" s="18">
-        <v>28.070175438596</v>
+        <v>-32.894736842105</v>
       </c>
       <c r="F21" s="17">
-        <v>265</v>
+        <v>248</v>
       </c>
       <c r="G21" s="17">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="H21" s="18">
-        <v>15.217391304347</v>
+        <v>-1.195219123505</v>
       </c>
       <c r="I21" s="17">
-        <v>926</v>
+        <v>977</v>
       </c>
       <c r="J21" s="17">
-        <v>948</v>
+        <v>1024</v>
       </c>
       <c r="K21" s="18">
-        <v>-2.320675105485</v>
+        <v>-4.58984375</v>
       </c>
       <c r="L21" s="18">
-        <v>-10.358180058083</v>
+        <v>-11.181818181818</v>
       </c>
       <c r="M21" s="18">
-        <v>17.961783439490</v>
+        <v>16.866028708134</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.588364434687</v>
+        <v>-74.877860632553</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>4</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E23" s="15">
-        <v>33.333333333333</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G23" s="14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H23" s="15">
-        <v>12.5</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="I23" s="14">
         <v>31</v>
       </c>
       <c r="J23" s="14">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="K23" s="15">
-        <v>-18.421052631578</v>
+        <v>-31.111111111111</v>
       </c>
       <c r="L23" s="15">
-        <v>-6.060606060606</v>
+        <v>-11.428571428571</v>
       </c>
       <c r="M23" s="15">
-        <v>106.666666666667</v>
+        <v>93.75</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D24" s="14">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="E24" s="15">
-        <v>-26.136363636363</v>
+        <v>-11.688311688311</v>
       </c>
       <c r="F24" s="14">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G24" s="14">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="H24" s="15">
-        <v>-22.713864306784</v>
+        <v>-20.241691842900</v>
       </c>
       <c r="I24" s="14">
-        <v>895</v>
+        <v>965</v>
       </c>
       <c r="J24" s="14">
-        <v>1297</v>
+        <v>1374</v>
       </c>
       <c r="K24" s="15">
-        <v>-30.994602929838</v>
+        <v>-29.767103347889</v>
       </c>
       <c r="L24" s="15">
-        <v>-31.990881458966</v>
+        <v>-30.774748923959</v>
       </c>
       <c r="M24" s="15">
-        <v>-8.766564729867</v>
+        <v>-8.962264150943</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D25" s="14">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="E25" s="15">
-        <v>-57.894736842105</v>
+        <v>-4.761904761904</v>
       </c>
       <c r="F25" s="14">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="G25" s="14">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="H25" s="15">
-        <v>-44.897959183673</v>
+        <v>-36.756756756756</v>
       </c>
       <c r="I25" s="14">
-        <v>429</v>
+        <v>469</v>
       </c>
       <c r="J25" s="14">
-        <v>767</v>
+        <v>809</v>
       </c>
       <c r="K25" s="15">
-        <v>-44.067796610169</v>
+        <v>-42.027194066749</v>
       </c>
       <c r="L25" s="15">
-        <v>-42.338709677419</v>
+        <v>-40.557667934093</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="D26" s="14">
         <v>44</v>
       </c>
       <c r="E26" s="15">
-        <v>-6.818181818181</v>
+        <v>-43.181818181818</v>
       </c>
       <c r="F26" s="14">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="G26" s="14">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H26" s="15">
-        <v>-9.677419354838</v>
+        <v>-12.738853503184</v>
       </c>
       <c r="I26" s="14">
-        <v>488</v>
+        <v>513</v>
       </c>
       <c r="J26" s="14">
-        <v>535</v>
+        <v>579</v>
       </c>
       <c r="K26" s="15">
-        <v>-8.785046728971</v>
+        <v>-11.398963730569</v>
       </c>
       <c r="L26" s="15">
-        <v>-5.973025048169</v>
+        <v>-7.733812949640</v>
       </c>
       <c r="M26" s="15">
-        <v>-10.622710622710</v>
+        <v>-12.307692307692</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
+        <v>2</v>
+      </c>
+      <c r="D27" s="14">
         <v>3</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
       <c r="E27" s="15">
-        <v>200</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F27" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G27" s="14">
         <v>8</v>
       </c>
       <c r="H27" s="15">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J27" s="14">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K27" s="15">
-        <v>43.333333333333</v>
+        <v>36.363636363636</v>
       </c>
       <c r="L27" s="15">
-        <v>34.375</v>
+        <v>36.363636363636</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D28" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E28" s="15">
-        <v>-33.333333333333</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F28" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G28" s="14">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H28" s="15">
-        <v>-6.25</v>
+        <v>-15</v>
       </c>
       <c r="I28" s="14">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J28" s="14">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="K28" s="15">
-        <v>-10.769230769230</v>
+        <v>-15.277777777777</v>
       </c>
       <c r="L28" s="15">
-        <v>7.407407407407</v>
+        <v>10.909090909090</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1467,7 +1467,7 @@
         <v>36</v>
       </c>
       <c r="C29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1476,31 +1476,31 @@
         <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>2</v>
-      </c>
-      <c r="G29" s="14">
-        <v>1</v>
-      </c>
-      <c r="H29" s="15">
-        <v>100</v>
+        <v>4</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J29" s="14">
         <v>3</v>
       </c>
       <c r="K29" s="15">
-        <v>66.666666666666</v>
+        <v>133.333333333333</v>
       </c>
       <c r="L29" s="15">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M29" s="15">
-        <v>-58.333333333333</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="N29" s="15">
-        <v>-75</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1517,31 +1517,31 @@
         <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>2</v>
-      </c>
-      <c r="G30" s="14">
-        <v>1</v>
-      </c>
-      <c r="H30" s="15">
-        <v>100</v>
+        <v>3</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J30" s="14">
         <v>3</v>
       </c>
       <c r="K30" s="15">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="L30" s="15">
         <v>0</v>
       </c>
       <c r="M30" s="15">
-        <v>-50</v>
+        <v>-40</v>
       </c>
       <c r="N30" s="15">
-        <v>-72.222222222222</v>
+        <v>-68.421052631578</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,11 +1551,11 @@
       <c r="C31" s="14">
         <v>1</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>0</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="14">
         <v>2</v>
@@ -1567,16 +1567,16 @@
         <v>100</v>
       </c>
       <c r="I31" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J31" s="14">
         <v>3</v>
       </c>
       <c r="K31" s="15">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="L31" s="15">
-        <v>-37.5</v>
+        <v>-25</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-pbsi.xlsx
+++ b/data/source/weekly/cs-en-us-pbsi.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -892,82 +892,82 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" s="15">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G15" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H15" s="15">
-        <v>-12.5</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I15" s="14">
         <v>33</v>
       </c>
       <c r="J15" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K15" s="15">
-        <v>32</v>
+        <v>22.222222222222</v>
       </c>
       <c r="L15" s="15">
-        <v>73.684210526315</v>
+        <v>57.142857142857</v>
       </c>
       <c r="M15" s="15">
-        <v>73.684210526315</v>
+        <v>65</v>
       </c>
       <c r="N15" s="15">
-        <v>17.857142857142</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>8</v>
       </c>
       <c r="D16" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E16" s="15">
-        <v>-100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G16" s="14">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H16" s="15">
-        <v>5.555555555555</v>
+        <v>13.636363636363</v>
       </c>
       <c r="I16" s="14">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J16" s="14">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="K16" s="15">
-        <v>-4.878048780487</v>
+        <v>-2.272727272727</v>
       </c>
       <c r="L16" s="15">
-        <v>-24.271844660194</v>
+        <v>-21.100917431192</v>
       </c>
       <c r="M16" s="15">
-        <v>-33.898305084745</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N16" s="15">
-        <v>-82.471910112359</v>
+        <v>-81.779661016949</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D17" s="14">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="E17" s="15">
-        <v>-50</v>
+        <v>9.523809523809</v>
       </c>
       <c r="F17" s="14">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G17" s="14">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H17" s="15">
-        <v>-15.730337078651</v>
+        <v>-15.555555555555</v>
       </c>
       <c r="I17" s="14">
-        <v>302</v>
+        <v>325</v>
       </c>
       <c r="J17" s="14">
-        <v>312</v>
+        <v>333</v>
       </c>
       <c r="K17" s="15">
-        <v>-3.205128205128</v>
+        <v>-2.402402402402</v>
       </c>
       <c r="L17" s="15">
-        <v>-6.211180124223</v>
+        <v>-4.970760233918</v>
       </c>
       <c r="M17" s="15">
-        <v>83.030303030303</v>
+        <v>88.953488372093</v>
       </c>
       <c r="N17" s="15">
-        <v>-9.850746268656</v>
+        <v>-7.932011331444</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>7</v>
-      </c>
-      <c r="D18" s="14">
-        <v>9</v>
-      </c>
-      <c r="E18" s="15">
-        <v>-22.222222222222</v>
+        <v>5</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
         <v>20</v>
       </c>
       <c r="G18" s="14">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H18" s="15">
-        <v>-16.666666666666</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I18" s="14">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="J18" s="14">
         <v>131</v>
       </c>
       <c r="K18" s="15">
-        <v>-45.038167938931</v>
+        <v>-40.458015267175</v>
       </c>
       <c r="L18" s="15">
-        <v>-20</v>
+        <v>-16.129032258064</v>
       </c>
       <c r="M18" s="15">
-        <v>-56.363636363636</v>
+        <v>-54.651162790697</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.036750483559</v>
+        <v>-93.035714285714</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D19" s="14">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="E19" s="15">
-        <v>4</v>
+        <v>3.030303030303</v>
       </c>
       <c r="F19" s="14">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="G19" s="14">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H19" s="15">
-        <v>3.030303030303</v>
+        <v>9.615384615384</v>
       </c>
       <c r="I19" s="14">
-        <v>420</v>
+        <v>456</v>
       </c>
       <c r="J19" s="14">
-        <v>412</v>
+        <v>445</v>
       </c>
       <c r="K19" s="15">
-        <v>1.941747572815</v>
+        <v>2.471910112359</v>
       </c>
       <c r="L19" s="15">
-        <v>-13.580246913580</v>
+        <v>-13.142857142857</v>
       </c>
       <c r="M19" s="15">
-        <v>49.466192170818</v>
+        <v>51.495016611295</v>
       </c>
       <c r="N19" s="15">
-        <v>-13.580246913580</v>
+        <v>-11.456310679611</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>-50</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F20" s="14">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="G20" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H20" s="15">
-        <v>92.307692307692</v>
+        <v>54.545454545454</v>
       </c>
       <c r="I20" s="14">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="J20" s="14">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K20" s="15">
-        <v>20</v>
+        <v>22.222222222222</v>
       </c>
       <c r="L20" s="15">
-        <v>-8.860759493670</v>
+        <v>-7.228915662650</v>
       </c>
       <c r="M20" s="15">
-        <v>-16.279069767441</v>
+        <v>-18.947368421052</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.366795366795</v>
+        <v>-95.330503335354</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="D21" s="17">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="E21" s="18">
-        <v>-32.894736842105</v>
+        <v>15.384615384615</v>
       </c>
       <c r="F21" s="17">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="G21" s="17">
         <v>251</v>
       </c>
       <c r="H21" s="18">
-        <v>-1.195219123505</v>
+        <v>2.788844621513</v>
       </c>
       <c r="I21" s="17">
-        <v>977</v>
+        <v>1055</v>
       </c>
       <c r="J21" s="17">
-        <v>1024</v>
+        <v>1089</v>
       </c>
       <c r="K21" s="18">
-        <v>-4.58984375</v>
+        <v>-3.122130394857</v>
       </c>
       <c r="L21" s="18">
-        <v>-11.181818181818</v>
+        <v>-10.136286201022</v>
       </c>
       <c r="M21" s="18">
-        <v>16.866028708134</v>
+        <v>18.406285072951</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.877860632553</v>
+        <v>-74.566055930569</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="14">
+        <v>4</v>
       </c>
       <c r="D23" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E23" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F23" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G23" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H23" s="15">
-        <v>-53.846153846153</v>
+        <v>-37.5</v>
       </c>
       <c r="I23" s="14">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J23" s="14">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K23" s="15">
-        <v>-31.111111111111</v>
+        <v>-26.530612244898</v>
       </c>
       <c r="L23" s="15">
-        <v>-11.428571428571</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="M23" s="15">
-        <v>93.75</v>
+        <v>100</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D24" s="14">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E24" s="15">
-        <v>-11.688311688311</v>
+        <v>-13.953488372093</v>
       </c>
       <c r="F24" s="14">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="G24" s="14">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="H24" s="15">
-        <v>-20.241691842900</v>
+        <v>-18.75</v>
       </c>
       <c r="I24" s="14">
-        <v>965</v>
+        <v>1038</v>
       </c>
       <c r="J24" s="14">
-        <v>1374</v>
+        <v>1460</v>
       </c>
       <c r="K24" s="15">
-        <v>-29.767103347889</v>
+        <v>-28.904109589041</v>
       </c>
       <c r="L24" s="15">
-        <v>-30.774748923959</v>
+        <v>-29.579375848032</v>
       </c>
       <c r="M24" s="15">
-        <v>-8.962264150943</v>
+        <v>-9.895833333333</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D25" s="14">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="E25" s="15">
-        <v>-4.761904761904</v>
+        <v>-48.4375</v>
       </c>
       <c r="F25" s="14">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="G25" s="14">
-        <v>185</v>
+        <v>207</v>
       </c>
       <c r="H25" s="15">
-        <v>-36.756756756756</v>
+        <v>-38.164251207729</v>
       </c>
       <c r="I25" s="14">
-        <v>469</v>
+        <v>502</v>
       </c>
       <c r="J25" s="14">
-        <v>809</v>
+        <v>873</v>
       </c>
       <c r="K25" s="15">
-        <v>-42.027194066749</v>
+        <v>-42.497136311569</v>
       </c>
       <c r="L25" s="15">
-        <v>-40.557667934093</v>
+        <v>-39.225181598063</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D26" s="14">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E26" s="15">
-        <v>-43.181818181818</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="G26" s="14">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H26" s="15">
-        <v>-12.738853503184</v>
+        <v>-23.636363636363</v>
       </c>
       <c r="I26" s="14">
-        <v>513</v>
+        <v>549</v>
       </c>
       <c r="J26" s="14">
-        <v>579</v>
+        <v>621</v>
       </c>
       <c r="K26" s="15">
-        <v>-11.398963730569</v>
+        <v>-11.594202898550</v>
       </c>
       <c r="L26" s="15">
-        <v>-7.733812949640</v>
+        <v>-8.955223880597</v>
       </c>
       <c r="M26" s="15">
-        <v>-12.307692307692</v>
+        <v>-11.165048543689</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
         <v>2</v>
       </c>
-      <c r="D27" s="14">
-        <v>3</v>
-      </c>
       <c r="E27" s="15">
-        <v>-33.333333333333</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G27" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I27" s="14">
         <v>45</v>
       </c>
       <c r="J27" s="14">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K27" s="15">
-        <v>36.363636363636</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L27" s="15">
-        <v>36.363636363636</v>
+        <v>25</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D28" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E28" s="15">
-        <v>-57.142857142857</v>
+        <v>-60</v>
       </c>
       <c r="F28" s="14">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G28" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H28" s="15">
-        <v>-15</v>
+        <v>-38.095238095238</v>
       </c>
       <c r="I28" s="14">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J28" s="14">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="K28" s="15">
-        <v>-15.277777777777</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="L28" s="15">
-        <v>10.909090909090</v>
+        <v>6.779661016949</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>2</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1497,18 +1497,18 @@
         <v>16.666666666666</v>
       </c>
       <c r="M29" s="15">
-        <v>-41.666666666666</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="N29" s="15">
-        <v>-66.666666666666</v>
+        <v>-68.181818181818</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1538,45 +1538,45 @@
         <v>0</v>
       </c>
       <c r="M30" s="15">
-        <v>-40</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="N30" s="15">
-        <v>-68.421052631578</v>
+        <v>-70</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
+      <c r="C31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="14">
         <v>1</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="14">
+        <v>4</v>
+      </c>
+      <c r="G31" s="14">
         <v>2</v>
-      </c>
-      <c r="G31" s="14">
-        <v>1</v>
       </c>
       <c r="H31" s="15">
         <v>100</v>
       </c>
       <c r="I31" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J31" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K31" s="15">
         <v>100</v>
       </c>
       <c r="L31" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="14">
+        <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1617,7 +1617,7 @@
         <v>21</v>
       </c>
       <c r="F33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
@@ -1626,16 +1626,16 @@
         <v>21</v>
       </c>
       <c r="I33" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J33" s="14">
         <v>2</v>
       </c>
       <c r="K33" s="15">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="L33" s="15">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-pbsi.xlsx
+++ b/data/source/weekly/cs-en-us-pbsi.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -896,37 +896,37 @@
         <v>20</v>
       </c>
       <c r="D15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="15">
         <v>-100</v>
       </c>
       <c r="F15" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G15" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H15" s="15">
-        <v>-33.333333333333</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I15" s="14">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J15" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K15" s="15">
-        <v>22.222222222222</v>
+        <v>21.428571428571</v>
       </c>
       <c r="L15" s="15">
-        <v>57.142857142857</v>
+        <v>61.904761904761</v>
       </c>
       <c r="M15" s="15">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="N15" s="15">
-        <v>10</v>
+        <v>-5.555555555555</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>11</v>
+      </c>
+      <c r="D16" s="14">
         <v>8</v>
       </c>
-      <c r="D16" s="14">
-        <v>6</v>
-      </c>
       <c r="E16" s="15">
-        <v>33.333333333333</v>
+        <v>37.5</v>
       </c>
       <c r="F16" s="14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G16" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H16" s="15">
-        <v>13.636363636363</v>
+        <v>21.739130434782</v>
       </c>
       <c r="I16" s="14">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="J16" s="14">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="K16" s="15">
-        <v>-2.272727272727</v>
+        <v>1.041666666666</v>
       </c>
       <c r="L16" s="15">
-        <v>-21.100917431192</v>
+        <v>-15.652173913043</v>
       </c>
       <c r="M16" s="15">
-        <v>-33.333333333333</v>
+        <v>-27.611940298507</v>
       </c>
       <c r="N16" s="15">
-        <v>-81.779661016949</v>
+        <v>-80.324543610547</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,37 +978,37 @@
         <v>23</v>
       </c>
       <c r="D17" s="14">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E17" s="15">
-        <v>9.523809523809</v>
+        <v>35.294117647058</v>
       </c>
       <c r="F17" s="14">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G17" s="14">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="H17" s="15">
-        <v>-15.555555555555</v>
+        <v>-9.677419354838</v>
       </c>
       <c r="I17" s="14">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="J17" s="14">
-        <v>333</v>
+        <v>350</v>
       </c>
       <c r="K17" s="15">
-        <v>-2.402402402402</v>
+        <v>-0.571428571428</v>
       </c>
       <c r="L17" s="15">
-        <v>-4.970760233918</v>
+        <v>-2.521008403361</v>
       </c>
       <c r="M17" s="15">
-        <v>88.953488372093</v>
+        <v>97.727272727272</v>
       </c>
       <c r="N17" s="15">
-        <v>-7.932011331444</v>
+        <v>-6.451612903225</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>4</v>
+      </c>
+      <c r="D18" s="14">
         <v>5</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="E18" s="15">
+        <v>-20</v>
       </c>
       <c r="F18" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G18" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H18" s="15">
-        <v>33.333333333333</v>
+        <v>23.529411764705</v>
       </c>
       <c r="I18" s="14">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="J18" s="14">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="K18" s="15">
-        <v>-40.458015267175</v>
+        <v>-38.970588235294</v>
       </c>
       <c r="L18" s="15">
-        <v>-16.129032258064</v>
+        <v>-15.306122448979</v>
       </c>
       <c r="M18" s="15">
-        <v>-54.651162790697</v>
+        <v>-53.888888888888</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.035714285714</v>
+        <v>-93.048576214405</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D19" s="14">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E19" s="15">
-        <v>3.030303030303</v>
+        <v>7.407407407407</v>
       </c>
       <c r="F19" s="14">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G19" s="14">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="H19" s="15">
-        <v>9.615384615384</v>
+        <v>5.504587155963</v>
       </c>
       <c r="I19" s="14">
-        <v>456</v>
+        <v>483</v>
       </c>
       <c r="J19" s="14">
-        <v>445</v>
+        <v>472</v>
       </c>
       <c r="K19" s="15">
-        <v>2.471910112359</v>
+        <v>2.330508474576</v>
       </c>
       <c r="L19" s="15">
-        <v>-13.142857142857</v>
+        <v>-14.664310954063</v>
       </c>
       <c r="M19" s="15">
-        <v>51.495016611295</v>
+        <v>49.074074074074</v>
       </c>
       <c r="N19" s="15">
-        <v>-11.456310679611</v>
+        <v>-9.719626168224</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E20" s="15">
-        <v>66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G20" s="14">
         <v>11</v>
       </c>
       <c r="H20" s="15">
-        <v>54.545454545454</v>
+        <v>63.636363636363</v>
       </c>
       <c r="I20" s="14">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="J20" s="14">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K20" s="15">
-        <v>22.222222222222</v>
+        <v>20.895522388059</v>
       </c>
       <c r="L20" s="15">
-        <v>-7.228915662650</v>
+        <v>-7.954545454545</v>
       </c>
       <c r="M20" s="15">
-        <v>-18.947368421052</v>
+        <v>-19.801980198019</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.330503335354</v>
+        <v>-95.320623916811</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D21" s="17">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E21" s="18">
-        <v>15.384615384615</v>
+        <v>14.516129032258</v>
       </c>
       <c r="F21" s="17">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="G21" s="17">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="H21" s="18">
-        <v>2.788844621513</v>
+        <v>4.230769230769</v>
       </c>
       <c r="I21" s="17">
-        <v>1055</v>
+        <v>1126</v>
       </c>
       <c r="J21" s="17">
-        <v>1089</v>
+        <v>1151</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.122130394857</v>
+        <v>-2.172024326672</v>
       </c>
       <c r="L21" s="18">
-        <v>-10.136286201022</v>
+        <v>-9.630818619582</v>
       </c>
       <c r="M21" s="18">
-        <v>18.406285072951</v>
+        <v>20.17075773746</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.566055930569</v>
+        <v>-74.233409610984</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D23" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="F23" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G23" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H23" s="15">
-        <v>-37.5</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="I23" s="14">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J23" s="14">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="K23" s="15">
-        <v>-26.530612244898</v>
+        <v>-25.925925925925</v>
       </c>
       <c r="L23" s="15">
-        <v>-7.692307692307</v>
+        <v>-2.439024390243</v>
       </c>
       <c r="M23" s="15">
-        <v>100</v>
+        <v>122.222222222222</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="D24" s="14">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="E24" s="15">
-        <v>-13.953488372093</v>
+        <v>-30.666666666666</v>
       </c>
       <c r="F24" s="14">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="G24" s="14">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="H24" s="15">
-        <v>-18.75</v>
+        <v>-20.245398773006</v>
       </c>
       <c r="I24" s="14">
-        <v>1038</v>
+        <v>1090</v>
       </c>
       <c r="J24" s="14">
-        <v>1460</v>
+        <v>1535</v>
       </c>
       <c r="K24" s="15">
-        <v>-28.904109589041</v>
+        <v>-28.990228013029</v>
       </c>
       <c r="L24" s="15">
-        <v>-29.579375848032</v>
+        <v>-29.813264649066</v>
       </c>
       <c r="M24" s="15">
-        <v>-9.895833333333</v>
+        <v>-11.237785016286</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="D25" s="14">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="E25" s="15">
-        <v>-48.4375</v>
+        <v>-48.648648648648</v>
       </c>
       <c r="F25" s="14">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="G25" s="14">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="H25" s="15">
-        <v>-38.164251207729</v>
+        <v>-42</v>
       </c>
       <c r="I25" s="14">
-        <v>502</v>
+        <v>521</v>
       </c>
       <c r="J25" s="14">
-        <v>873</v>
+        <v>910</v>
       </c>
       <c r="K25" s="15">
-        <v>-42.497136311569</v>
+        <v>-42.747252747252</v>
       </c>
       <c r="L25" s="15">
-        <v>-39.225181598063</v>
+        <v>-39.907727797001</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D26" s="14">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="E26" s="15">
-        <v>-16.666666666666</v>
+        <v>-32.653061224489</v>
       </c>
       <c r="F26" s="14">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="G26" s="14">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="H26" s="15">
-        <v>-23.636363636363</v>
+        <v>-24.581005586592</v>
       </c>
       <c r="I26" s="14">
-        <v>549</v>
+        <v>583</v>
       </c>
       <c r="J26" s="14">
-        <v>621</v>
+        <v>670</v>
       </c>
       <c r="K26" s="15">
-        <v>-11.594202898550</v>
+        <v>-12.985074626865</v>
       </c>
       <c r="L26" s="15">
-        <v>-8.955223880597</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="M26" s="15">
-        <v>-11.165048543689</v>
+        <v>-12.462462462462</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,31 +1388,31 @@
         <v>20</v>
       </c>
       <c r="D27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" s="15">
         <v>-100</v>
       </c>
       <c r="F27" s="14">
+        <v>6</v>
+      </c>
+      <c r="G27" s="14">
         <v>7</v>
       </c>
-      <c r="G27" s="14">
-        <v>9</v>
-      </c>
       <c r="H27" s="15">
-        <v>-22.222222222222</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I27" s="14">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J27" s="14">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K27" s="15">
-        <v>28.571428571428</v>
+        <v>27.777777777777</v>
       </c>
       <c r="L27" s="15">
-        <v>25</v>
+        <v>21.052631578947</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D28" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E28" s="15">
-        <v>-60</v>
+        <v>-37.5</v>
       </c>
       <c r="F28" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G28" s="14">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H28" s="15">
-        <v>-38.095238095238</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="I28" s="14">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="J28" s="14">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K28" s="15">
-        <v>-18.181818181818</v>
+        <v>-20</v>
       </c>
       <c r="L28" s="15">
-        <v>6.779661016949</v>
+        <v>4.615384615384</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1476,7 +1476,7 @@
         <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1500,7 +1500,7 @@
         <v>-46.153846153846</v>
       </c>
       <c r="N29" s="15">
-        <v>-68.181818181818</v>
+        <v>-72</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1517,7 +1517,7 @@
         <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1541,42 +1541,42 @@
         <v>-45.454545454545</v>
       </c>
       <c r="N30" s="15">
-        <v>-70</v>
+        <v>-73.913043478260</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="14">
+        <v>1</v>
+      </c>
+      <c r="D31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G31" s="14">
         <v>2</v>
       </c>
       <c r="H31" s="15">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="I31" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J31" s="14">
         <v>4</v>
       </c>
       <c r="K31" s="15">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="L31" s="15">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
